--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644889D4-D417-4E88-A44C-80EF5B851FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E57E089-BBB7-43F8-B381-FA9AC4C74A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>46.88</v>
+        <v>45.93</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23737.588567520001</v>
+        <v>23256.558082470001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13270740447385121</v>
+        <v>0.14060796047169277</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4511,7 +4511,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.6138637170302019E-2</v>
+        <v>4.7092952548307393E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.1331058020477814E-2</v>
+        <v>2.1772262138036142E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7257757078580571</v>
+        <v>1.7257757078580573</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13483,20 +13483,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.1331058020477814E-2</v>
+        <v>2.1772262138036142E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1331058020477814E-2</v>
+        <v>2.1772262138036142E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1331058020477814E-2</v>
+        <v>2.1772262138036142E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.0665529010238907E-2</v>
+        <v>1.0886131069018071E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14682,50 +14682,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6138637170302019E-2</v>
+        <v>4.7092952548307393E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.6899834612589262E-2</v>
+        <v>6.8283567311956991E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.6625890185901024E-2</v>
+        <v>6.8003956714893107E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.2333292036301179E-2</v>
+        <v>4.3208898991112549E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.9706465112654292E-2</v>
+        <v>4.0527739701311412E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.7850649995902099E-2</v>
+        <v>2.8426703065706299E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.6560579052890956E-2</v>
+        <v>2.7109948748084655E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6565053518228443E-2</v>
+        <v>1.6907679271381437E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2397638798183371E-2</v>
+        <v>1.265406720789977E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.1137020547475931E-3</v>
+        <v>6.240155722328917E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.9618208367079005E-3</v>
+        <v>4.0437657484186026E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14739,43 +14739,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8626953338849397E-2</v>
+        <v>7.0046409155786193E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8657756818432845E-2</v>
+        <v>8.0284686254041629E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2964098793096194E-2</v>
+        <v>5.4059589623782919E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7260035301572542E-2</v>
+        <v>3.8030708794637942E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7978418747586647E-2</v>
+        <v>2.8557114541407837E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9239753441076453E-2</v>
+        <v>2.9844538239008581E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0240829039282537E-2</v>
+        <v>2.0659483243230248E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1928151008035683E-2</v>
+        <v>1.2174868697076263E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3716495044248587E-3</v>
+        <v>7.5241221155549175E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2975249209628482E-3</v>
+        <v>5.4070970671617315E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.88</v>
+        <v>-45.93</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.88</v>
+        <v>45.93</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19274,7 +19274,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7257757078580571</v>
+        <v>1.7257757078580573</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19333,7 +19333,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.88</v>
+        <v>45.93</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19346,7 +19346,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13270740447385121</v>
+        <v>0.14060796047169277</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E57E089-BBB7-43F8-B381-FA9AC4C74A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02A2686-3FE1-4B51-9BB9-EC44E2375D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>1462055536.8163233</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>213032611</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-213032611.00000003</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>9271615.2714172397</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-10773913</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-1502297.7285827603</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-194943.10109087895</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-365138309.77193511</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>1588040749.2687776</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>1095219986.2147145</v>
       </c>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.22405670341828193</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.24330033263324671</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.42456310191863128</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.50794527810050039</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.5295422156001708</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.5295422156001706</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>533481194.11000001</v>
       </c>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>5.3145118525683231E-2</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.36488435676778314</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>5078017354.46</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>4150855827.3182759</v>
       </c>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>125240754.68399999</v>
       </c>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7257757078580573</v>
+        <v>1.7257757078580571</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6017,411 +6033,411 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>7798913979</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>6311963850</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>5445152633</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>4939315985</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>2956758302</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>2389355321</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>1707538304</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>1139183826</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>694657422</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>479151199</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>5114327878</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>3915820963</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>3767200164</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>3505125804</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>1936776307</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>1447475772</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>1008193651</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>672472586</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>406608482</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>285219753</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>478714939</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>373685879</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>280986971</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>199250773</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>157114047</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>162036874</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>148533985</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>122587394</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>111709735</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>77990782</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>253881041</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>232460848</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>157533022</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>110815428</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>99736422</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>104708887</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>91880229</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>50830792</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>39460173</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>32507628</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>255918596</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>220006702</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>202331051</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>154945424</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>104720121</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>79166101</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>61487163</v>
       </c>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334">
+      <c r="C9" s="321">
         <v>-70283969</v>
       </c>
-      <c r="D9" s="334">
+      <c r="D9" s="321">
         <v>76220632</v>
       </c>
-      <c r="E9" s="334">
+      <c r="E9" s="321">
         <v>20133006</v>
       </c>
-      <c r="F9" s="334">
+      <c r="F9" s="321">
         <v>1499444</v>
       </c>
-      <c r="G9" s="334">
+      <c r="G9" s="321">
         <v>11085542</v>
       </c>
-      <c r="H9" s="334">
+      <c r="H9" s="321">
         <v>38861023</v>
       </c>
-      <c r="I9" s="334">
+      <c r="I9" s="321">
         <v>-12704453</v>
       </c>
-      <c r="J9" s="334">
-        <v>0</v>
-      </c>
-      <c r="K9" s="334">
-        <v>0</v>
-      </c>
-      <c r="L9" s="334">
-        <v>0</v>
-      </c>
-      <c r="M9" s="334"/>
+      <c r="J9" s="321">
+        <v>0</v>
+      </c>
+      <c r="K9" s="321">
+        <v>0</v>
+      </c>
+      <c r="L9" s="321">
+        <v>0</v>
+      </c>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>10773913</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>19213222</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>16787986</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>5280756</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>1093564</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>2759318</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>1307356</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>156551394</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>159297476</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>52423241</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>16165039</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>12495464</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>24748172</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>14095046</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>309204387</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>307004817</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>202660810</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>136628407</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>109313998</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>110812786</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>84670792</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>49833797</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>31011793</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>21880350</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>1629038383</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>1867145469</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>1257239986</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>884463388</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>664140193</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>694081237</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>480468472</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>283145541</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>174985183</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>125750467</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>233229</v>
       </c>
-      <c r="D16" s="334">
-        <v>0</v>
-      </c>
-      <c r="E16" s="334">
-        <v>0</v>
-      </c>
-      <c r="F16" s="334">
-        <v>0</v>
-      </c>
-      <c r="G16" s="334">
-        <v>0</v>
-      </c>
-      <c r="H16" s="334">
-        <v>0</v>
-      </c>
-      <c r="I16" s="334">
-        <v>0</v>
-      </c>
-      <c r="J16" s="334">
-        <v>0</v>
-      </c>
-      <c r="K16" s="334">
+      <c r="D16" s="321">
+        <v>0</v>
+      </c>
+      <c r="E16" s="321">
+        <v>0</v>
+      </c>
+      <c r="F16" s="321">
+        <v>0</v>
+      </c>
+      <c r="G16" s="321">
+        <v>0</v>
+      </c>
+      <c r="H16" s="321">
+        <v>0</v>
+      </c>
+      <c r="I16" s="321">
+        <v>0</v>
+      </c>
+      <c r="J16" s="321">
+        <v>0</v>
+      </c>
+      <c r="K16" s="321">
         <v>202868</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>16241</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6433,171 +6449,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>213032611</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>135475921</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>104602959</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>78877993</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>40782935</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>28330776</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>25091208</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>1916547999</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>2227397039</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>936702406</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>373661725</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>891764853</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>696158346</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>415714136</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>348706422</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>142342727</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>112359422</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-178527168</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-862617775</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-1221538814</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-69051239</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-707286524</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-666330101</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>156611794</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-1034615747</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-185922892</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-345198556</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-996799146</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-520447150</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>44534961</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>2069283867</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-192224576</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>147431845</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>83396087</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>893792882</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-14815942</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>409943115</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6637,186 +6653,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>2470363699.1300001</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>2391271680</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>2078427810</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>1620191874</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>635971724</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>797615199</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>525650211</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>299236277</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>180459802</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>105834918</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>2342136338.9299998</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>1921374942</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>1795225840</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>1387177645</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>941597028</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>460791109</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>359087239</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>243055593</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>179108332</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>137707371</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>5315649326.7300005</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>5242067251</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>4736625835</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>3596300871</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>2124874675</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>1651958950</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>1032202540</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>576053698</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>285486746</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>172274845</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>10038197465.91</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>8965233891</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>7065182676</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>5978168759</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>3744157600</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>3207493644</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>2601382187</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>2202505763</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>1085805361</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>922655590</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>2901653.62</v>
       </c>
-      <c r="D32" s="334">
-        <v>0</v>
-      </c>
-      <c r="E32" s="334">
-        <v>0</v>
-      </c>
-      <c r="F32" s="334">
-        <v>0</v>
-      </c>
-      <c r="G32" s="334">
-        <v>0</v>
-      </c>
-      <c r="H32" s="334">
-        <v>0</v>
-      </c>
-      <c r="I32" s="334">
-        <v>0</v>
-      </c>
-      <c r="J32" s="334">
-        <v>0</v>
-      </c>
-      <c r="K32" s="334">
-        <v>0</v>
-      </c>
-      <c r="L32" s="334">
+      <c r="D32" s="321">
+        <v>0</v>
+      </c>
+      <c r="E32" s="321">
+        <v>0</v>
+      </c>
+      <c r="F32" s="321">
+        <v>0</v>
+      </c>
+      <c r="G32" s="321">
+        <v>0</v>
+      </c>
+      <c r="H32" s="321">
+        <v>0</v>
+      </c>
+      <c r="I32" s="321">
+        <v>0</v>
+      </c>
+      <c r="J32" s="321">
+        <v>0</v>
+      </c>
+      <c r="K32" s="321">
+        <v>0</v>
+      </c>
+      <c r="L32" s="321">
         <v>6016241</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6843,47 +6859,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>7798913979</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>6311963850</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>5445152633</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>4939315985</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>2956758302</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>2389355321</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>1707538304</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>1139183826</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>694657422</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>479151199</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6892,47 +6908,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-5114327878</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-3915820963</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-3767200164</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-3505125804</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-1936776307</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-1447475772</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-1008193651</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-672472586</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-406608482</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-285219753</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6941,47 +6957,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>2684586101</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>2396142887</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>1677952469</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>1434190181</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>1019981995</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>941879549</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>699344653</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>466711240</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>288048940</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>193931446</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6990,47 +7006,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-478714939</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-373685879</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-280986971</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-199250773</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-157114047</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-162036874</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-148533985</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-122587394</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-111709735</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-77990782</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7039,47 +7055,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-253881041</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-232460848</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-157533022</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-110815428</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-99736422</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-104708887</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-91880229</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-50830792</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-39460173</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-32507628</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7088,47 +7104,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-224833898</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-141225031</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-123453949</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-88435345</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-57377625</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-57327987</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-56653756</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-71756602</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-72249562</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-45483154</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7137,47 +7153,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-255918596</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-220006702</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-202331051</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-154945424</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-104720121</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-79166101</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-61487163</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7186,47 +7202,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>1949952566</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1802450306</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>1194634447</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>1079993984</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>758147827</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>700676574</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>489323505</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>344123846</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>176339205</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>115940664</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7333,47 +7349,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-309204387</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-307004817</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-202660810</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-136628407</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-109313998</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-110812786</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-84670792</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-49833797</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-31011793</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-21880350</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7382,47 +7398,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>1629038383</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>1867145469</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>1257239986</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>884463388</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>664140193</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>694081237</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>480468472</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>283145541</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>174985183</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>125750467</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7431,47 +7447,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-233229</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>-202868</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-16241</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7485,47 +7501,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-10773913</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-19213222</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-16787986</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-5280756</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-1093564</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-2759318</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-1307356</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7534,47 +7550,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>156551394</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>159297476</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>52423241</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>16165039</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>12495464</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>24748172</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>14095046</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7790,47 +7806,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-213032611</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-135475921</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-104602959</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-78877993</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-40782935</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-28330776</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-25091208</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7839,47 +7855,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-213032611</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-135475921</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-104602959</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-78877993</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-40782935</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-28330776</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-25091208</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7888,47 +7904,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7937,47 +7953,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>741221685</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>844332114</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>-240301447</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>2373894353</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>-7746247</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>177260090</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>655722017</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>207883557</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>-58396107</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>177103981</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8359,115 +8375,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>2470363699.1300001</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>2391271680</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>2078427810</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>1620191874</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>635971724</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>797615199</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>2342136338.9299998</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>1921374942</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>1795225840</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>1387177645</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>941597028</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>460791109</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>5315649326.7300005</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>5242067251</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>4736625835</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>3596300871</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>2124874675</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>1651958950</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>1032202540</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>576053698</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>285486746</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>172274845</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8476,47 +8492,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>10038197465.91</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>8965233891</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>7065182676</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>5978168759</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>3744157600</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>3207493644</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>2601382187</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>2202505763</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>1085805361</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>922655590</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9600,11 +9616,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-529609107.66666669</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-463580763.570862</v>
       </c>
@@ -9632,8 +9648,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>927161527.14172399</v>
       </c>
@@ -9937,54 +9953,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:I4)</f>
         <v>6518676820.666667</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>7798913979</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>6311963850</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>5445152633</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>4939315985</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>2956758302</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>2389355321</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>1707538304</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>1139183826</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>694657422</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>479151199</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9994,52 +10010,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-4575868789.8503437</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5368208919</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-4148281811</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-3924733186</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-3615941232</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-2036512729</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-1552184659</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-1100073880</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-723303378</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-446068655</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-317727381</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10049,52 +10065,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>1942808030.8163233</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>2430705060</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>2163682039</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>1520419447</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>1323374753</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>920245573</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>837170662</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>607464424</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>415880448</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>248588767</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>161423818</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10104,52 +10120,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-480752494</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-480752494</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-361231733</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-325785000</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-243380769</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-162097746</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-136494088</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-118140919</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-71756602</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-72249562</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-45483154</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10159,54 +10175,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>1462055536.8163233</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>1949952566</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1802450306</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>1194634447</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>1079993984</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>758147827</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>700676574</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>489323505</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>344123846</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>176339205</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>115940664</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10216,52 +10232,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>213032611</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>213032611</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>135475921</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>104602959</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>78877993</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>40782935</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>28330776</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>25091208</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10271,52 +10287,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-213032611.00000003</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-213032611</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-135475921</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-104602959</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-78877993</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-40782935</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-28330776</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-25091208</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10326,54 +10342,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>-70283969</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>76220632</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>20133006</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>1499444</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>11085542</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>38861023</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>-12704453</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10383,52 +10399,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-1502297.7285827603</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>17809768.268777564</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>9871848.1776871048</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-7216373.9336116798</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-2329288.6852256656</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>1187899.9407266113</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>1759286.672615598</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>1266165.0146564273</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10438,52 +10454,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>1460553239.0877404</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1897478365.2687776</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1888542786.1776872</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1207551079.0663884</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>1079164139.3147743</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>770421268.94072664</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>741296883.67261565</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>477885217.01465642</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>344123846</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>176339205</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>115940664</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10493,52 +10509,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-365138309.77193511</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-309204387</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-307004817</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-202660810</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-136628407</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-109313998</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-110812786</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-84670792</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-49833797</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-31011793</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-21880350</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10548,54 +10564,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-194943.10109087895</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-233229</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>-202868</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-16241</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10605,54 +10621,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>1095219986.2147145</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>1588040749.2687776</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>1581537969.1776872</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>1004890269.0663884</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>942535732.31477427</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>661107270.94072664</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>630484097.67261565</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>393214425.01465642</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>294290049</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>145124544</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>94044073</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10662,7 +10678,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10671,24 +10687,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10696,71 +10712,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>1095219986.2147145</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>1588040749.2687776</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>1581537969.1776872</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>1004890269.0663884</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>942535732.31477427</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>661107270.94072664</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>630484097.67261565</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>393214425.01465642</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>294290049</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>145124544</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>94044073</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10833,54 +10849,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-4363663800.5877705</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-5114327878</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-3915820963</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-3767200164</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-3505125804</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-1936776307</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-1447475772</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-1008193651</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-672472586</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-406608482</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-285219753</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10890,54 +10906,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-212204989.26257277</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-253881041</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-232460848</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-157533022</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-110815428</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-99736422</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-104708887</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-91880229</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-50830792</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-39460173</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-32507628</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10947,54 +10963,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-4575868789.8503437</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-5368208919</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-4148281811</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-3924733186</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-3615941232</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-2036512729</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-1552184659</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-1100073880</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-723303378</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-446068655</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-317727381</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11200,54 +11216,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>G33</f>
         <v>-224833898</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-224833898</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-141225031</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-123453949</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-88435345</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-57377625</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-57327987</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-56653756</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-71756602</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-72249562</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-45483154</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11257,7 +11273,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>G34</f>
         <v>-255918596</v>
       </c>
@@ -11266,47 +11282,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-255918596</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-220006702</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-202331051</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-154945424</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-104720121</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-79166101</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-61487163</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11316,54 +11332,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-480752494</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-480752494</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-361231733</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-325785000</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-243380769</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-162097746</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-136494088</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-118140919</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-71756602</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-72249562</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-45483154</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11657,52 +11673,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-10773913</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-10773913</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-19213222</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-16787986</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-5280756</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-1093564</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-2759318</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-1307356</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11712,52 +11728,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>9271615.2714172397</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>28583681.268777564</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>29085070.177687105</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>9571612.0663883202</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>2951467.3147743344</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>2281463.9407266113</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>4518604.672615598</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>2573521.0146564273</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11767,54 +11783,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>50780173.544600002</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>156551394</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>159297476</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>52423241</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>16165039</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>12495464</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>24748172</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>14095046</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11824,52 +11840,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-1502297.7285827603</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>17809768.268777564</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>9871848.1776871048</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-7216373.9336116798</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-2329288.6852256656</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>1187899.9407266113</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>1759286.672615598</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>1266165.0146564273</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -12015,52 +12031,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12070,52 +12086,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>-70283969</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>76220632</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>20133006</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>1499444</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>11085542</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>38861023</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>-12704453</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12125,52 +12141,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12180,52 +12196,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>-70283969</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>76220632</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>20133006</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>1499444</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>11085542</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>38861023</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>-12704453</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12235,53 +12251,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-87203308</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>155395094</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>209498088</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-71285916</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-7181078</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>43367572</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>75732522</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-11144508</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>29657771</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>31690153</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12291,52 +12307,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-157487277</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>231615726</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>229631094</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-69786472</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>3904464</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>82228595</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>63028069</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-11144508</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>29657771</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>31690153</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13711,54 +13727,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>15353846792.640001</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>15353846792.639999</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>14207301142</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>11801808511</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>9574469630</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>5869032275</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>4859452594</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>3633584727</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>2778559461</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>1371292107</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>1094930435</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13768,54 +13784,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>2470363699.1300001</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>2391271680</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>2078427810</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>1620191874</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>635971724</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>797615199</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13825,54 +13841,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>2342136338.9299998</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>1921374942</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>1795225840</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1387177645</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>941597028</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>460791109</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13882,54 +13898,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>5315649326.7300005</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>5315649326.7300005</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>5242067251</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>4736625835</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>3596300871</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>2124874675</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>1651958950</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>1032202540</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>576053698</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>285486746</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>172274845</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13939,54 +13955,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>10038197465.91</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>10038197465.91</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>8965233891</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>7065182676</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>5978168759</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>3744157600</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>3207493644</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>2601382187</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>2202505763</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>1085805361</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>922655590</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15484,7 +15500,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15523,7 +15539,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>1095219986.2147145</v>
       </c>
@@ -15555,7 +15571,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>18253666436.911911</v>
       </c>
@@ -15563,17 +15579,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>533481194.11000001</v>
       </c>
@@ -15581,15 +15597,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>4150855827.3182759</v>
       </c>
@@ -15597,15 +15613,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>125240754.68399999</v>
       </c>
@@ -15613,15 +15629,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>21996281824.804184</v>
       </c>
@@ -15688,7 +15704,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15698,7 +15714,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15712,10 +15728,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15733,7 +15749,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15755,7 +15771,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15777,7 +15793,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15797,9 +15813,19 @@
         <f t="shared" si="1"/>
         <v>1041897147.1568592</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15819,9 +15845,19 @@
         <f t="shared" si="1"/>
         <v>1024706155.4087249</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15841,9 +15877,19 @@
         <f t="shared" si="1"/>
         <v>1007798809.8900584</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15865,7 +15911,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15887,7 +15933,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15909,7 +15955,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15931,7 +15977,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15953,7 +15999,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15975,7 +16021,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15997,11 +16043,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>1881681255.7311022</v>
       </c>
@@ -16017,13 +16063,23 @@
         <f t="shared" si="1"/>
         <v>882205600.10892165</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>1961672121.627439</v>
       </c>
@@ -16039,13 +16095,23 @@
         <f t="shared" si="1"/>
         <v>867649471.19253528</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>2045063424.5570717</v>
       </c>
@@ -16061,9 +16127,19 @@
         <f t="shared" si="1"/>
         <v>853333514.0558387</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16085,7 +16161,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16107,7 +16183,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16129,7 +16205,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16151,7 +16227,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16173,7 +16249,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16195,7 +16271,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16217,7 +16293,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16239,7 +16315,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16261,7 +16337,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16283,7 +16359,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16305,11 +16381,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>3370319851.3699865</v>
       </c>
@@ -16325,13 +16401,23 @@
         <f t="shared" si="1"/>
         <v>698896324.07377934</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>3513593215.250072</v>
       </c>
@@ -16347,13 +16433,23 @@
         <f t="shared" si="1"/>
         <v>687364743.46360135</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>3662957175.1871381</v>
       </c>
@@ -16369,13 +16465,23 @@
         <f t="shared" si="1"/>
         <v>676023430.48939252</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>3818670644.3477669</v>
       </c>
@@ -16391,9 +16497,19 @@
         <f t="shared" si="1"/>
         <v>664869245.79198575</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16415,7 +16531,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16426,11 +16542,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16440,7 +16556,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>28965236773.442753</v>
@@ -16467,7 +16583,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16489,7 +16605,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16510,14 +16626,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>18253666436.911896</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>20013084336.720451</v>
       </c>
       <c r="D58" s="123">
@@ -16529,16 +16645,26 @@
       <c r="F58" s="123">
         <v>27366348701.915016</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>18253666436.911896</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>20793717528.359291</v>
       </c>
       <c r="D59" s="123">
@@ -16550,16 +16676,26 @@
       <c r="F59" s="123">
         <v>32956420591.122528</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>18253666436.911892</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>21590480648.473019</v>
       </c>
       <c r="D60" s="123">
@@ -16571,16 +16707,26 @@
       <c r="F60" s="123">
         <v>39823276180.631668</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>18253666436.911892</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>22361954115.932011</v>
       </c>
       <c r="D61" s="123">
@@ -16592,26 +16738,56 @@
       <c r="F61" s="123">
         <v>47907714791.933189</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16983,6 +17159,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17085,7 +17331,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>8439131316.666667</v>
       </c>
@@ -17093,8 +17339,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18551,7 +18797,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>1949952566</v>
       </c>
@@ -18559,11 +18805,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 浙江鼎力(603338.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18576,7 +18822,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>1588040749.2687776</v>
       </c>
@@ -18584,8 +18830,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18598,7 +18844,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>1095219986.2147145</v>
       </c>
@@ -18606,8 +18852,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18617,8 +18863,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18631,8 +18877,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18650,8 +18896,8 @@
         <v>0.16445427582528804</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18668,8 +18914,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.21768298308972489</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18686,8 +18932,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.18992961357468019</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18713,21 +18959,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18741,8 +18987,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18756,8 +19002,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18777,8 +19023,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18788,8 +19034,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18803,8 +19049,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18814,8 +19060,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18835,8 +19081,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18846,8 +19092,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18861,8 +19107,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18872,8 +19118,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18893,8 +19139,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18904,8 +19150,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18919,8 +19165,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18931,8 +19177,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18994,8 +19240,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19005,8 +19251,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19020,8 +19266,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19031,8 +19277,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19052,8 +19298,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19063,8 +19309,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19078,8 +19324,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19089,8 +19335,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19274,7 +19520,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19283,7 +19529,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7257757078580573</v>
+        <v>1.7257757078580571</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02A2686-3FE1-4B51-9BB9-EC44E2375D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9471CDC5-C313-4185-A4D2-61D07FC657B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>45.93</v>
+        <v>45.34</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23256.558082470001</v>
+        <v>22957.81283386</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14060796047169277</v>
+        <v>0.14562654231140892</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.7092952548307393E-2</v>
+        <v>4.7705763355618845E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.1772262138036142E-2</v>
+        <v>2.2055580061755623E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7257757078580571</v>
+        <v>1.7257757078580573</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13499,20 +13499,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.1772262138036142E-2</v>
+        <v>2.2055580061755623E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1772262138036142E-2</v>
+        <v>2.2055580061755623E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1772262138036142E-2</v>
+        <v>2.2055580061755623E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.0886131069018071E-2</v>
+        <v>1.1027790030877812E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14698,50 +14698,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7092952548307393E-2</v>
+        <v>4.7705763355618845E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8283567311956991E-2</v>
+        <v>6.9172127186550164E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8003956714893107E-2</v>
+        <v>6.8888878074879575E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.3208898991112549E-2</v>
+        <v>4.3771167416449035E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.0527739701311412E-2</v>
+        <v>4.1055118757856925E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.8426703065706299E-2</v>
+        <v>2.8796613846667186E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7109948748084655E-2</v>
+        <v>2.7462724878683901E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6907679271381437E-2</v>
+        <v>1.7127695388940215E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.265406720789977E-2</v>
+        <v>1.2818731955422064E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.240155722328917E-3</v>
+        <v>6.3213575722665888E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.0437657484186026E-3</v>
+        <v>4.096386431955589E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14755,43 +14755,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0046409155786193E-2</v>
+        <v>7.0957908525038818E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0284686254041629E-2</v>
+        <v>8.1329414196032901E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4059589623782919E-2</v>
+        <v>5.4763055831944185E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8030708794637942E-2</v>
+        <v>3.8525594506786963E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8557114541407837E-2</v>
+        <v>2.8928722339807277E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9844538239008581E-2</v>
+        <v>3.0232899014505162E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0659483243230248E-2</v>
+        <v>2.0928320806386531E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2174868697076263E-2</v>
+        <v>1.2333297733937204E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5241221155549175E-3</v>
+        <v>7.622031953406206E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4070970671617315E-3</v>
+        <v>5.4774584978989488E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.93</v>
+        <v>-45.34</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18981,7 +18981,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.93</v>
+        <v>45.34</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19520,7 +19520,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19529,7 +19529,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7257757078580571</v>
+        <v>1.7257757078580573</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.93</v>
+        <v>45.34</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14060796047169277</v>
+        <v>0.14562654231140892</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB15AD2-1A00-45BC-A98C-ED37078F8F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C304FAD-AB08-A24D-8AF0-050D474613FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.35</v>
+        <v>46.51</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22962.876312650002</v>
+        <v>23550.239852289997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4481,14 +4492,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1455407482695299</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.1357585521591167</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.7695243892916392E-2</v>
+        <v>4.650568287559146E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.2050716648291068E-2</v>
+        <v>2.1500752526338422E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>0.46232527288881309</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>0.18902580584937359</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>0.24330033263324671</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.50794527810050039</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.5295422156001706</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>5.3145118525683231E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>0.36488435676778314</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7257757078580571</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>1.7257757078580573</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>27.077488023189172</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.55491894710083656</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>2.1501253634045896</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>38.694606751139908</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.36884873378671179</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>2.6730119494616398</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>54.335666470913992</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>0.11907612787712119</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>2.5448900584493499</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>50.386473310255305</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.18057341576207186</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6199,7 +6210,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6235,7 +6246,7 @@
       </c>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6251,7 +6262,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6267,7 +6278,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6297,7 +6308,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6327,7 +6338,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6363,7 +6374,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6399,7 +6410,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6435,13 +6446,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6471,7 +6482,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6487,7 +6498,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6503,7 +6514,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6539,7 +6550,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6575,7 +6586,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6611,7 +6622,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6637,7 +6648,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6645,7 +6656,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6682,7 +6693,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6719,7 +6730,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6756,7 +6767,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6793,7 +6804,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6830,7 +6841,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6846,12 +6857,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6900,7 +6911,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6949,7 +6960,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6998,7 +7009,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7047,7 +7058,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7096,7 +7107,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7145,7 +7156,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7194,7 +7205,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7243,7 +7254,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7292,7 +7303,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7341,7 +7352,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7390,7 +7401,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7439,7 +7450,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7488,12 +7499,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7542,7 +7553,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7591,12 +7602,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7645,7 +7656,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7694,7 +7705,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7743,7 +7754,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7792,13 +7803,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7847,7 +7858,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7896,7 +7907,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7945,7 +7956,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7994,7 +8005,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8043,12 +8054,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8098,7 +8109,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8147,7 +8158,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8197,7 +8208,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8246,7 +8257,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8296,7 +8307,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8312,13 +8323,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8367,7 +8378,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8401,7 +8412,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8435,7 +8446,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8484,7 +8495,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8565,18 +8576,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8592,7 +8603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8603,7 +8614,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8623,7 +8634,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8645,7 +8656,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8666,7 +8677,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8687,7 +8698,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8708,7 +8719,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8729,7 +8740,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8750,7 +8761,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8762,7 +8773,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8775,7 +8786,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8799,12 +8810,12 @@
         <v>4695456373.698</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8824,7 +8835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8844,7 +8855,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8864,7 +8875,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8884,7 +8895,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8904,7 +8915,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8925,7 +8936,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8945,7 +8956,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8965,7 +8976,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8977,7 +8988,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8990,7 +9001,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9014,7 +9025,7 @@
         <v>24520798.362</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9031,7 +9042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9050,7 +9061,7 @@
         <v>2842625029.8935003</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9065,7 +9076,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9084,7 +9095,7 @@
         <v>2839723376.2735004</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9100,7 +9111,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9117,7 +9128,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9137,7 +9148,7 @@
         <v>8158274356.6235008</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9148,7 +9159,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9161,7 +9172,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9180,7 +9191,7 @@
         <v>3438297184.5634999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9196,7 +9207,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9212,7 +9223,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9228,7 +9239,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9247,7 +9258,7 @@
         <v>190941844.41999999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9267,7 +9278,7 @@
         <v>4719977172.0600004</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9287,7 +9298,7 @@
         <v>4594736417.3760004</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9306,7 +9317,7 @@
         <v>125240754.68399999</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9317,7 +9328,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9331,7 +9342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9345,7 +9356,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9360,10 +9371,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9376,7 +9387,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9390,7 +9401,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9401,10 +9412,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9416,7 +9427,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9430,7 +9441,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9444,10 +9455,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9459,7 +9470,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9470,7 +9481,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9481,10 +9492,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9496,7 +9507,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9512,7 +9523,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9523,7 +9534,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9537,7 +9548,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9553,7 +9564,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9563,7 +9574,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9573,7 +9584,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9583,7 +9594,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9593,10 +9604,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9608,7 +9619,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9624,7 +9635,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9640,7 +9651,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9653,7 +9664,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9666,10 +9677,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9681,7 +9692,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9695,7 +9706,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9709,7 +9720,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9723,7 +9734,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9737,7 +9748,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9748,7 +9759,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9756,7 +9767,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9773,7 +9784,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9790,7 +9801,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9807,7 +9818,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9838,19 +9849,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9907,7 +9918,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9930,7 +9941,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9944,7 +9955,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -10001,7 +10012,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10056,7 +10067,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10111,7 +10122,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10166,7 +10177,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10223,7 +10234,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10278,7 +10289,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10333,7 +10344,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10390,7 +10401,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10445,7 +10456,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10500,7 +10511,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10555,7 +10566,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10612,7 +10623,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10669,7 +10680,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10695,7 +10706,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10720,7 +10731,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10777,7 +10788,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10796,7 +10807,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10819,7 +10830,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10840,7 +10851,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10897,7 +10908,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10954,7 +10965,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11011,18 +11022,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11081,7 +11092,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11141,7 +11152,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11196,18 +11207,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11264,7 +11275,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11323,7 +11334,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11380,18 +11391,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11449,7 +11460,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11507,7 +11518,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11562,18 +11573,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11631,10 +11642,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11657,14 +11668,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11719,7 +11730,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11774,7 +11785,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11831,7 +11842,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11886,11 +11897,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11900,7 +11911,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11926,7 +11937,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11953,7 +11964,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11985,7 +11996,7 @@
       </c>
       <c r="L55" s="42">
         <f t="shared" si="21"/>
-        <v>253.93107064861681</v>
+        <v>253.93107064861678</v>
       </c>
       <c r="M55" s="42">
         <f t="shared" si="21"/>
@@ -12008,11 +12019,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12022,7 +12033,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12077,7 +12088,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12132,7 +12143,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12187,7 +12198,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12242,7 +12253,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12298,7 +12309,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12353,11 +12364,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12367,7 +12378,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12392,7 +12403,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12417,7 +12428,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12442,7 +12453,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12469,10 +12480,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12495,7 +12506,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12516,7 +12527,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12573,7 +12584,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12630,7 +12641,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12687,7 +12698,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12744,7 +12755,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12801,7 +12812,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12860,7 +12871,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12917,7 +12928,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12974,7 +12985,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13031,7 +13042,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13088,7 +13099,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13146,7 +13157,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13203,7 +13214,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13229,7 +13240,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13253,7 +13264,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13310,18 +13321,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13377,7 +13388,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13433,7 +13444,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13488,27 +13499,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.2050716648291068E-2</v>
+        <v>2.1500752526338422E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.2050716648291068E-2</v>
+        <v>2.1500752526338422E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2050716648291068E-2</v>
+        <v>2.1500752526338422E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.1025358324145534E-2</v>
+        <v>1.0750376263169211E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13543,11 +13554,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13568,7 +13579,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13625,7 +13636,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13682,10 +13693,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13708,7 +13719,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13718,7 +13729,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13775,7 +13786,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13832,7 +13843,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13889,7 +13900,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13946,7 +13957,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -14003,11 +14014,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14030,7 +14041,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14087,7 +14098,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14144,7 +14155,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14171,18 +14182,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14234,7 +14245,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14286,11 +14297,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14344,7 +14355,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14399,7 +14410,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14453,7 +14464,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14509,7 +14520,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14566,7 +14577,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14585,7 +14596,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14608,7 +14619,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14629,7 +14640,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14687,795 +14698,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7695243892916392E-2</v>
+        <v>4.650568287559146E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9156874236784668E-2</v>
+        <v>6.7432041424170822E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8873687583573096E-2</v>
+        <v>6.7155917693292627E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.3761515560348387E-2</v>
+        <v>4.2670065161509341E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.1046065809950016E-2</v>
+        <v>4.0022341098284953E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.8790263986943558E-2</v>
+        <v>2.8072209671208138E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7456669151037005E-2</v>
+        <v>2.6771875854644769E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.7123918609361619E-2</v>
+        <v>1.6696833131252406E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.281590533316067E-2</v>
+        <v>1.2496265466756321E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.319963667620004E-3</v>
+        <v>6.1623382568601849E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.0954831493906592E-3</v>
+        <v>3.9933382245724881E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0942261797690406E-2</v>
+        <v>6.9172899860788228E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1311480477356826E-2</v>
+        <v>7.928350117497597E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4750980185674737E-2</v>
+        <v>5.3385442946040633E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8517099337105197E-2</v>
+        <v>3.7556449256884991E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8922343349214154E-2</v>
+        <v>2.8200994858887597E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0226232443608909E-2</v>
+        <v>2.9472363821063521E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0923705961666268E-2</v>
+        <v>2.040185047004011E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2330578153400502E-2</v>
+        <v>1.2023042770516296E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6203512407373173E-3</v>
+        <v>7.430293028755911E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4762506790460488E-3</v>
+        <v>5.3396682067241097E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15497,16 +15508,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15518,7 +15529,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15531,7 +15542,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15552,7 +15563,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15563,7 +15574,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15581,7 +15592,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15597,7 +15608,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15613,7 +15624,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15629,7 +15640,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15643,7 +15654,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15657,7 +15668,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15671,10 +15682,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15684,13 +15695,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15700,7 +15711,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15710,7 +15721,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15724,10 +15735,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15745,7 +15756,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15767,7 +15778,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15789,7 +15800,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15821,7 +15832,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15853,7 +15864,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15885,7 +15896,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15907,7 +15918,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15929,7 +15940,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15951,7 +15962,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15973,7 +15984,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15995,7 +16006,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16017,7 +16028,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16039,7 +16050,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16071,7 +16082,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16103,7 +16114,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16135,7 +16146,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16157,7 +16168,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16179,7 +16190,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16201,7 +16212,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16223,7 +16234,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16245,7 +16256,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16267,7 +16278,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16289,7 +16300,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16311,7 +16322,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16333,7 +16344,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16355,7 +16366,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16377,7 +16388,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16409,7 +16420,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16441,7 +16452,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16473,7 +16484,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16505,7 +16516,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16527,7 +16538,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16538,11 +16549,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16552,7 +16563,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>28965236773.442753</v>
@@ -16579,7 +16590,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16601,7 +16612,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16622,7 +16633,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16653,7 +16664,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16684,7 +16695,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16715,7 +16726,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16746,7 +16757,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16763,7 +16774,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16783,7 +16794,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16806,7 +16817,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16832,7 +16843,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16859,7 +16870,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16886,7 +16897,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16913,7 +16924,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16940,7 +16951,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16966,7 +16977,7 @@
         <v>86.039447137733433</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16992,7 +17003,7 @@
         <v>102.00562167226035</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17009,7 +17020,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17031,7 +17042,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17054,7 +17065,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17077,7 +17088,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17100,7 +17111,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17122,14 +17133,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17137,26 +17148,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17170,7 +17181,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17184,7 +17195,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17198,7 +17209,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17212,7 +17223,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17257,16 +17268,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17278,7 +17289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17291,7 +17302,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17312,7 +17323,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17323,7 +17334,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17339,7 +17350,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17353,10 +17364,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17366,13 +17377,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17382,7 +17393,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17392,7 +17403,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17406,10 +17417,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17427,7 +17438,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17449,7 +17460,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17471,7 +17482,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17493,7 +17504,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17515,7 +17526,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17537,7 +17548,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17559,7 +17570,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17581,7 +17592,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17603,7 +17614,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17625,7 +17636,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17647,7 +17658,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17669,7 +17680,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17691,7 +17702,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17713,7 +17724,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17735,7 +17746,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17757,7 +17768,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17779,7 +17790,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17801,7 +17812,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17823,7 +17834,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17845,7 +17856,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17867,7 +17878,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17889,7 +17900,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17911,7 +17922,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17933,7 +17944,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17955,7 +17966,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17977,7 +17988,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17999,7 +18010,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18021,7 +18032,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18043,7 +18054,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18065,7 +18076,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18087,7 +18098,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18109,7 +18120,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18120,11 +18131,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18134,7 +18145,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>13391360995.571005</v>
@@ -18161,7 +18172,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18183,7 +18194,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18204,7 +18215,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18225,7 +18236,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18246,7 +18257,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18267,7 +18278,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18288,14 +18299,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18305,7 +18316,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18328,7 +18339,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18354,7 +18365,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18381,7 +18392,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18408,7 +18419,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18435,7 +18446,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18462,7 +18473,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18488,7 +18499,7 @@
         <v>36.360983804056005</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18514,7 +18525,7 @@
         <v>43.742549802721591</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18531,7 +18542,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18553,7 +18564,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18576,7 +18587,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18599,7 +18610,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18622,7 +18633,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18644,14 +18655,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18659,23 +18670,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18705,17 +18716,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18728,7 +18739,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18737,10 +18748,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.35</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-46.51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18760,7 +18771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18769,7 +18780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18789,7 +18800,7 @@
         <v>65.714648137522119</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18814,7 +18825,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18836,7 +18847,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18858,7 +18869,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18869,7 +18880,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18883,7 +18894,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18902,7 +18913,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18920,7 +18931,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18931,7 +18942,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18940,7 +18951,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18948,7 +18959,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18960,24 +18971,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.35</v>
+        <v>46.51</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18997,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -19001,7 +19012,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19010,7 +19021,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19022,7 +19033,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19033,7 +19044,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19048,7 +19059,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19059,7 +19070,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19068,7 +19079,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19080,7 +19091,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19091,7 +19102,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19106,7 +19117,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19117,7 +19128,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19126,7 +19137,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19138,7 +19149,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19149,7 +19160,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19164,7 +19175,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19176,7 +19187,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19189,7 +19200,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19198,12 +19209,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19213,12 +19224,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19227,7 +19238,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19239,7 +19250,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19250,7 +19261,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19265,7 +19276,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19276,7 +19287,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19285,7 +19296,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19297,7 +19308,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19308,7 +19319,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19323,7 +19334,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19334,7 +19345,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19354,7 +19365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19363,7 +19374,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19371,7 +19382,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19384,7 +19395,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19396,7 +19407,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19412,7 +19423,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19420,7 +19431,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19430,7 +19441,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19442,7 +19453,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19452,7 +19463,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19468,7 +19479,7 @@
         <v>0.11421512240685464</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19477,12 +19488,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19492,7 +19503,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19505,33 +19516,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7257757078580571</v>
+        <v>1.7257757078580573</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19541,7 +19552,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19561,45 +19572,45 @@
         <v>0.55491894710083656</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.35</v>
+        <v>46.51</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1455407482695299</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.1357585521591167</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19608,7 +19619,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19620,7 +19631,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19630,7 +19641,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19650,14 +19661,14 @@
         <v>0.36884873378671179</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19668,7 +19679,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19680,7 +19691,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19692,7 +19703,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19711,15 +19722,15 @@
         <v>0.11907612787712119</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19728,7 +19739,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19738,7 +19749,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19748,7 +19759,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19767,16 +19778,16 @@
         <v>0.18057341576207186</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19784,7 +19795,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19792,7 +19803,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C304FAD-AB08-A24D-8AF0-050D474613FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4858FB57-A961-411B-907D-D0F7A3D24E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>46.51</v>
+        <v>45.87</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23550.239852289997</v>
+        <v>23226.177209729998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1357585521591167</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.14111433989680933</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.650568287559146E-2</v>
+        <v>4.7154552224629574E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.1500752526338422E-2</v>
+        <v>2.1800741225201658E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>0.46232527288881309</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>0.18902580584937359</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>0.24330033263324671</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>0.50794527810050039</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>1.5295422156001706</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>5.3145118525683231E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>0.36488435676778314</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>1.7257757078580573</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>27.077488023189172</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.55491894710083656</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>2.1501253634045896</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>38.694606751139908</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.36884873378671179</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>2.6730119494616398</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>54.335666470913992</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>0.11907612787712119</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>2.5448900584493499</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>50.386473310255305</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.18057341576207186</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6210,7 +6199,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6246,7 +6235,7 @@
       </c>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6262,7 +6251,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6278,7 +6267,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6308,7 +6297,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6338,7 +6327,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6374,7 +6363,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6410,7 +6399,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6446,13 +6435,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6482,7 +6471,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6498,7 +6487,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6514,7 +6503,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6550,7 +6539,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6586,7 +6575,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6622,7 +6611,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6648,7 +6637,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6656,7 +6645,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6693,7 +6682,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6730,7 +6719,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6767,7 +6756,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6804,7 +6793,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6841,7 +6830,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6857,12 +6846,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6911,7 +6900,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6960,7 +6949,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -7009,7 +6998,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7058,7 +7047,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7107,7 +7096,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7156,7 +7145,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7205,7 +7194,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7254,7 +7243,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7303,7 +7292,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7352,7 +7341,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7401,7 +7390,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7450,7 +7439,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7499,12 +7488,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7553,7 +7542,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7602,12 +7591,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7656,7 +7645,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7705,7 +7694,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7754,7 +7743,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7803,13 +7792,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7858,7 +7847,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7907,7 +7896,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7956,7 +7945,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -8005,7 +7994,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8054,12 +8043,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8109,7 +8098,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8158,7 +8147,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8208,7 +8197,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8257,7 +8246,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8307,7 +8296,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8323,13 +8312,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8378,7 +8367,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8412,7 +8401,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8446,7 +8435,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8495,7 +8484,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8576,7 +8565,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8587,7 +8576,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8603,7 +8592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8614,7 +8603,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8634,7 +8623,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8656,7 +8645,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8677,7 +8666,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8698,7 +8687,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8719,7 +8708,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8740,7 +8729,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8761,7 +8750,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8773,7 +8762,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8786,7 +8775,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8810,12 +8799,12 @@
         <v>4695456373.698</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8835,7 +8824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8855,7 +8844,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8875,7 +8864,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8895,7 +8884,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8915,7 +8904,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8936,7 +8925,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8956,7 +8945,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8976,7 +8965,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8988,7 +8977,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -9001,7 +8990,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9025,7 +9014,7 @@
         <v>24520798.362</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9042,7 +9031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9061,7 +9050,7 @@
         <v>2842625029.8935003</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9076,7 +9065,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9095,7 +9084,7 @@
         <v>2839723376.2735004</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9111,7 +9100,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9128,7 +9117,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9148,7 +9137,7 @@
         <v>8158274356.6235008</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9159,7 +9148,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9172,7 +9161,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9191,7 +9180,7 @@
         <v>3438297184.5634999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9207,7 +9196,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9223,7 +9212,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9239,7 +9228,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9258,7 +9247,7 @@
         <v>190941844.41999999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9278,7 +9267,7 @@
         <v>4719977172.0600004</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9298,7 +9287,7 @@
         <v>4594736417.3760004</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9317,7 +9306,7 @@
         <v>125240754.68399999</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9328,7 +9317,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9342,7 +9331,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9356,7 +9345,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9371,10 +9360,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9387,7 +9376,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9401,7 +9390,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9412,10 +9401,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9427,7 +9416,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9441,7 +9430,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9455,10 +9444,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9470,7 +9459,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9481,7 +9470,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9492,10 +9481,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9507,7 +9496,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9523,7 +9512,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9534,7 +9523,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9548,7 +9537,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9564,7 +9553,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9574,7 +9563,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9584,7 +9573,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9594,7 +9583,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9604,10 +9593,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9619,7 +9608,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9635,7 +9624,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9651,7 +9640,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9664,7 +9653,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9677,10 +9666,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9692,7 +9681,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9706,7 +9695,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9720,7 +9709,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9734,7 +9723,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9748,7 +9737,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9759,7 +9748,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9767,7 +9756,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9784,7 +9773,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9801,7 +9790,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9818,7 +9807,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9849,19 +9838,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9918,7 +9907,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9941,7 +9930,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9955,7 +9944,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -10012,7 +10001,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10067,7 +10056,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10122,7 +10111,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10177,7 +10166,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10234,7 +10223,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10289,7 +10278,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10344,7 +10333,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10401,7 +10390,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10456,7 +10445,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10511,7 +10500,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10566,7 +10555,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10623,7 +10612,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10680,7 +10669,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10706,7 +10695,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10731,7 +10720,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10788,7 +10777,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10807,7 +10796,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10830,7 +10819,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10851,7 +10840,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10908,7 +10897,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10965,7 +10954,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11022,18 +11011,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11092,7 +11081,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11152,7 +11141,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11207,18 +11196,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11275,7 +11264,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11334,7 +11323,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11391,18 +11380,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11460,7 +11449,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11518,7 +11507,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11573,18 +11562,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11642,10 +11631,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11668,14 +11657,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11730,7 +11719,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11785,7 +11774,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11842,7 +11831,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11897,11 +11886,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11911,7 +11900,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11937,7 +11926,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11964,7 +11953,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12019,11 +12008,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12033,7 +12022,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12088,7 +12077,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12143,7 +12132,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12198,7 +12187,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12253,7 +12242,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12309,7 +12298,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12364,11 +12353,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12378,7 +12367,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12403,7 +12392,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12428,7 +12417,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12453,7 +12442,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12480,10 +12469,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12506,7 +12495,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12527,7 +12516,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12584,7 +12573,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12641,7 +12630,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12698,7 +12687,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12755,7 +12744,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12812,7 +12801,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12871,7 +12860,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12928,7 +12917,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12985,7 +12974,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13042,7 +13031,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13099,7 +13088,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13157,7 +13146,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13214,7 +13203,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13240,7 +13229,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13264,7 +13253,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13321,18 +13310,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13388,7 +13377,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13444,7 +13433,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13499,27 +13488,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.1500752526338422E-2</v>
+        <v>2.1800741225201658E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1500752526338422E-2</v>
+        <v>2.1800741225201658E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1500752526338422E-2</v>
+        <v>2.1800741225201658E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.0750376263169211E-2</v>
+        <v>1.0900370612600829E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13554,11 +13543,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13579,7 +13568,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13636,7 +13625,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13693,10 +13682,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13719,7 +13708,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13729,7 +13718,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13786,7 +13775,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13843,7 +13832,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13900,7 +13889,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13957,7 +13946,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -14014,11 +14003,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14041,7 +14030,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14098,7 +14087,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14155,7 +14144,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14182,18 +14171,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14245,7 +14234,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14297,11 +14286,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14355,7 +14344,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14410,7 +14399,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14464,7 +14453,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14520,7 +14509,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14577,7 +14566,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14596,7 +14585,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14619,7 +14608,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14640,7 +14629,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14698,795 +14687,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.650568287559146E-2</v>
+        <v>4.7154552224629574E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.7432041424170822E-2</v>
+        <v>6.8372885254811097E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.7155917693292627E-2</v>
+        <v>6.8092908914650974E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.2670065161509341E-2</v>
+        <v>4.3265418152644418E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.0022341098284953E-2</v>
+        <v>4.0580751787251651E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.8072209671208138E-2</v>
+        <v>2.846388645755157E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.6771875854644769E-2</v>
+        <v>2.7145409766721786E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6696833131252406E-2</v>
+        <v>1.6929795267812284E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2496265466756321E-2</v>
+        <v>1.2670619290578514E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.1623382568601849E-3</v>
+        <v>6.2483181235353652E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.9933382245724881E-3</v>
+        <v>4.0490551738579994E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9172899860788228E-2</v>
+        <v>7.0138032974171788E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.928350117497597E-2</v>
+        <v>8.0389702194203883E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3385442946040633E-2</v>
+        <v>5.4130301971230643E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7556449256884991E-2</v>
+        <v>3.8080454653100518E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8200994858887597E-2</v>
+        <v>2.8594468517263178E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9472363821063521E-2</v>
+        <v>2.9883576222316636E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.040185047004011E-2</v>
+        <v>2.0686506766112174E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2023042770516296E-2</v>
+        <v>1.2190793966791211E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.430293028755911E-3</v>
+        <v>7.5339640019061998E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3396682067241097E-3</v>
+        <v>5.4141697905981763E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15508,16 +15497,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15529,7 +15518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15542,7 +15531,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15563,7 +15552,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15574,7 +15563,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15592,7 +15581,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15608,7 +15597,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15624,7 +15613,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15640,7 +15629,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15654,7 +15643,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15668,7 +15657,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15682,10 +15671,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15695,13 +15684,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15711,7 +15700,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15721,7 +15710,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15735,10 +15724,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15756,7 +15745,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15778,7 +15767,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15800,7 +15789,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15832,7 +15821,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15864,7 +15853,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15896,7 +15885,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15918,7 +15907,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15940,7 +15929,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15962,7 +15951,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15984,7 +15973,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -16006,7 +15995,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16028,7 +16017,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16050,7 +16039,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16082,7 +16071,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16114,7 +16103,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16146,7 +16135,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16168,7 +16157,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16190,7 +16179,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16212,7 +16201,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16234,7 +16223,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16256,7 +16245,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16278,7 +16267,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16300,7 +16289,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16322,7 +16311,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16344,7 +16333,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16366,7 +16355,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16388,7 +16377,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16420,7 +16409,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16452,7 +16441,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16484,7 +16473,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16516,7 +16505,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16538,7 +16527,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16549,11 +16538,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16563,7 +16552,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>28965236773.442753</v>
@@ -16590,7 +16579,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16612,7 +16601,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16633,7 +16622,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16664,7 +16653,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16695,7 +16684,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16726,7 +16715,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16757,7 +16746,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16774,7 +16763,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16794,7 +16783,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16817,7 +16806,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16843,7 +16832,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16870,7 +16859,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16897,7 +16886,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16924,7 +16913,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16951,7 +16940,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16977,7 +16966,7 @@
         <v>86.039447137733433</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -17003,7 +16992,7 @@
         <v>102.00562167226035</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17020,7 +17009,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17042,7 +17031,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17065,7 +17054,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17088,7 +17077,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17111,7 +17100,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17133,14 +17122,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17148,26 +17137,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17181,7 +17170,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17195,7 +17184,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17209,7 +17198,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17223,7 +17212,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17268,16 +17257,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17289,7 +17278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17302,7 +17291,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17323,7 +17312,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17334,7 +17323,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17350,7 +17339,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17364,10 +17353,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17377,13 +17366,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17393,7 +17382,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17403,7 +17392,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17417,10 +17406,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17438,7 +17427,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17460,7 +17449,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17482,7 +17471,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17504,7 +17493,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17526,7 +17515,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17548,7 +17537,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17570,7 +17559,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17592,7 +17581,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17614,7 +17603,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17636,7 +17625,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17658,7 +17647,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17680,7 +17669,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17702,7 +17691,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17724,7 +17713,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17746,7 +17735,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17768,7 +17757,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17790,7 +17779,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17812,7 +17801,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17834,7 +17823,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17856,7 +17845,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17878,7 +17867,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17900,7 +17889,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17922,7 +17911,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17944,7 +17933,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17966,7 +17955,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17988,7 +17977,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -18010,7 +17999,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18032,7 +18021,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18054,7 +18043,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18076,7 +18065,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18098,7 +18087,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18120,7 +18109,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18131,11 +18120,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18145,7 +18134,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>13391360995.571005</v>
@@ -18172,7 +18161,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18194,7 +18183,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18215,7 +18204,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18236,7 +18225,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18257,7 +18246,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18278,7 +18267,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18299,14 +18288,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18316,7 +18305,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18339,7 +18328,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18365,7 +18354,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18392,7 +18381,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18419,7 +18408,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18446,7 +18435,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18473,7 +18462,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18499,7 +18488,7 @@
         <v>36.360983804056005</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18525,7 +18514,7 @@
         <v>43.742549802721591</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18542,7 +18531,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18564,7 +18553,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18587,7 +18576,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18610,7 +18599,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18633,7 +18622,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18655,14 +18644,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18670,23 +18659,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18716,7 +18705,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18726,7 +18715,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18739,7 +18728,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18748,10 +18737,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.51</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-45.87</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18771,7 +18760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18780,7 +18769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18800,7 +18789,7 @@
         <v>65.714648137522119</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18825,7 +18814,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18847,7 +18836,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18869,7 +18858,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18880,7 +18869,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18894,7 +18883,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18913,7 +18902,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18931,7 +18920,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18942,7 +18931,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18951,7 +18940,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18959,7 +18948,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18971,24 +18960,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.51</v>
+        <v>45.87</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18997,7 +18986,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -19012,7 +19001,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19021,7 +19010,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19033,7 +19022,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19044,7 +19033,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19059,7 +19048,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19070,7 +19059,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19079,7 +19068,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19091,7 +19080,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19102,7 +19091,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19117,7 +19106,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19128,7 +19117,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19137,7 +19126,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19149,7 +19138,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19160,7 +19149,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19175,7 +19164,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19187,7 +19176,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19200,7 +19189,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19209,12 +19198,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19224,12 +19213,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19238,7 +19227,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19250,7 +19239,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19261,7 +19250,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19276,7 +19265,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19287,7 +19276,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19296,7 +19285,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19308,7 +19297,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19319,7 +19308,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19334,7 +19323,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19345,7 +19334,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19365,7 +19354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19374,7 +19363,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19382,7 +19371,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19395,7 +19384,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19407,7 +19396,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19423,7 +19412,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19431,7 +19420,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19441,7 +19430,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19453,7 +19442,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19463,7 +19452,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19479,7 +19468,7 @@
         <v>0.11421512240685464</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19488,12 +19477,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19503,7 +19492,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19516,12 +19505,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19530,7 +19519,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19542,7 +19531,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19552,7 +19541,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19572,45 +19561,45 @@
         <v>0.55491894710083656</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.51</v>
+        <v>45.87</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1357585521591167</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.14111433989680933</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19619,7 +19608,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19631,7 +19620,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19641,7 +19630,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19661,14 +19650,14 @@
         <v>0.36884873378671179</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19679,7 +19668,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19691,7 +19680,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19703,7 +19692,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19722,15 +19711,15 @@
         <v>0.11907612787712119</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19739,7 +19728,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19749,7 +19738,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19759,7 +19748,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19778,16 +19767,16 @@
         <v>0.18057341576207186</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19795,7 +19784,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19803,7 +19792,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4858FB57-A961-411B-907D-D0F7A3D24E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8DD114-CD29-4FF5-8587-1F3105638A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.87</v>
+        <v>47.46</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23226.177209729998</v>
+        <v>24031.27033734</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14111433989680933</v>
+        <v>0.12798936160593022</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.7154552224629574E-2</v>
+        <v>4.5574785304335411E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.1800741225201658E-2</v>
+        <v>2.1070375052675939E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.1800741225201658E-2</v>
+        <v>2.1070375052675939E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1800741225201658E-2</v>
+        <v>2.1070375052675939E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1800741225201658E-2</v>
+        <v>2.1070375052675939E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.0900370612600829E-2</v>
+        <v>1.0535187526337969E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7154552224629574E-2</v>
+        <v>4.5574785304335411E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8372885254811097E-2</v>
+        <v>6.6082263940964697E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8092908914650974E-2</v>
+        <v>6.5811667339128535E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.3265418152644418E-2</v>
+        <v>4.1815944598857971E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.0580751787251651E-2</v>
+        <v>3.9221219647729309E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.846388645755157E-2</v>
+        <v>2.7510292284194909E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7145409766721786E-2</v>
+        <v>2.6235987062779777E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6929795267812284E-2</v>
+        <v>1.6362615021798341E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2670619290578514E-2</v>
+        <v>1.2246129516621079E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2483181235353652E-3</v>
+        <v>6.0389876175003616E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.0490551738579994E-3</v>
+        <v>3.9134041471737546E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0138032974171788E-2</v>
+        <v>6.7788275864417616E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0389702194203883E-2</v>
+        <v>7.7696494724992252E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4130301971230643E-2</v>
+        <v>5.2316834206075628E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8080454653100518E-2</v>
+        <v>3.6804687208970094E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8594468517263178E-2</v>
+        <v>2.7636499597279013E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9883576222316636E-2</v>
+        <v>2.8882419749634725E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0686506766112174E-2</v>
+        <v>1.9993469560926368E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2190793966791211E-2</v>
+        <v>1.1782379251089608E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5339640019061998E-3</v>
+        <v>7.2815619209320977E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4141697905981763E-3</v>
+        <v>5.2327848355402089E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.87</v>
+        <v>-47.46</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.87</v>
+        <v>47.46</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.87</v>
+        <v>47.46</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14111433989680933</v>
+        <v>0.12798936160593022</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8DD114-CD29-4FF5-8587-1F3105638A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A064730E-FD76-4D31-95D4-6963BCB9E07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>47.46</v>
+        <v>45.26</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24031.27033734</v>
+        <v>22917.305003539997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12798936160593022</v>
+        <v>0.14631381557877776</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.5574785304335411E-2</v>
+        <v>4.7790086401762237E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.1070375052675939E-2</v>
+        <v>2.209456473707468E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.1070375052675939E-2</v>
+        <v>2.209456473707468E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1070375052675939E-2</v>
+        <v>2.209456473707468E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1070375052675939E-2</v>
+        <v>2.209456473707468E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.0535187526337969E-2</v>
+        <v>1.104728236853734E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.5574785304335411E-2</v>
+        <v>4.7790086401762237E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.6082263940964697E-2</v>
+        <v>6.9294393429920123E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.5811667339128535E-2</v>
+        <v>6.901064365698277E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.1815944598857971E-2</v>
+        <v>4.3848535807817043E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>3.9221219647729309E-2</v>
+        <v>4.1127686356191635E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.7510292284194909E-2</v>
+        <v>2.8847513738574689E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.6235987062779777E-2</v>
+        <v>2.7511267034898989E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6362615021798341E-2</v>
+        <v>1.7157969706905644E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2246129516621079E-2</v>
+        <v>1.2841389899664967E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.0389876175003616E-3</v>
+        <v>6.3325309837951212E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.9134041471737546E-3</v>
+        <v>4.1036270619723026E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7788275864417616E-2</v>
+        <v>7.1083331253319934E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7696494724992252E-2</v>
+        <v>8.1473169236591522E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2316834206075628E-2</v>
+        <v>5.4859853102526508E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6804687208970094E-2</v>
+        <v>3.8593691006136126E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7636499597279013E-2</v>
+        <v>2.8979855742087099E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8882419749634725E-2</v>
+        <v>3.0286337634062403E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9993469560926368E-2</v>
+        <v>2.0965312977498134E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1782379251089608E-2</v>
+        <v>1.2355097641553533E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2815619209320977E-3</v>
+        <v>7.6355043916800135E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2327848355402089E-3</v>
+        <v>5.4871402628090668E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.46</v>
+        <v>-45.26</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.46</v>
+        <v>45.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.46</v>
+        <v>45.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12798936160593022</v>
+        <v>0.14631381557877776</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A064730E-FD76-4D31-95D4-6963BCB9E07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC0AFD4-BD67-4683-A775-8A8E386D483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC0AFD4-BD67-4683-A775-8A8E386D483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D71F093-1F1D-4FE9-98A1-7EC4345590DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.26</v>
+        <v>44.79</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22917.305003539997</v>
+        <v>22679.321500409998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14631381557877776</v>
+        <v>0.15038493389693097</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.7790086401762237E-2</v>
+        <v>4.8291567549536923E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.209456473707468E-2</v>
+        <v>2.2326412145568207E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.209456473707468E-2</v>
+        <v>2.2326412145568207E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.209456473707468E-2</v>
+        <v>2.2326412145568207E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.209456473707468E-2</v>
+        <v>2.2326412145568207E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.104728236853734E-2</v>
+        <v>1.1163206072784104E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7790086401762237E-2</v>
+        <v>4.8291567549536923E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9294393429920123E-2</v>
+        <v>7.0021528167854091E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.901064365698277E-2</v>
+        <v>6.9734800891159632E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.3848535807817043E-2</v>
+        <v>4.4308656634556812E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.1127686356191635E-2</v>
+        <v>4.1559256183997167E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.8847513738574689E-2</v>
+        <v>2.9150222634692798E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7511267034898989E-2</v>
+        <v>2.7799954141538918E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.7157969706905644E-2</v>
+        <v>1.733801538143669E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2841389899664967E-2</v>
+        <v>1.297613991647324E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.3325309837951212E-3</v>
+        <v>6.3989808512294527E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.1036270619723026E-3</v>
+        <v>4.1466881184386338E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1083331253319934E-2</v>
+        <v>7.182923805593347E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1473169236591522E-2</v>
+        <v>8.2328100907526958E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4859853102526508E-2</v>
+        <v>5.5435520237114302E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8593691006136126E-2</v>
+        <v>3.8998670572398322E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8979855742087099E-2</v>
+        <v>2.9283953357599063E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0286337634062403E-2</v>
+        <v>3.0604144704569416E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0965312977498134E-2</v>
+        <v>2.1185310680097463E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2355097641553533E-2</v>
+        <v>1.2484744792514241E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6355043916800135E-3</v>
+        <v>7.7156268981343461E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4871402628090668E-3</v>
+        <v>5.5447190956628336E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.26</v>
+        <v>-44.79</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.26</v>
+        <v>44.79</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.26</v>
+        <v>44.79</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14631381557877776</v>
+        <v>0.15038493389693097</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D71F093-1F1D-4FE9-98A1-7EC4345590DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742B2030-A885-4BAD-8D97-572B1D1F3107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>44.79</v>
+        <v>44.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22679.321500409998</v>
+        <v>22532.480615500001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15038493389693097</v>
+        <v>0.15292578874872031</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.8291567549536923E-2</v>
+        <v>4.8606276641432779E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.2326412145568207E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.2326412145568207E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.2326412145568207E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2326412145568207E-2</v>
+        <v>2.247191011235955E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.1163206072784104E-2</v>
+        <v>1.1235955056179775E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8291567549536923E-2</v>
+        <v>4.8606276641432779E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.0021528167854091E-2</v>
+        <v>7.0477848239060337E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.9734800891159632E-2</v>
+        <v>7.0189252402585167E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.4308656634556812E-2</v>
+        <v>4.4597409677793243E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.1559256183997167E-2</v>
+        <v>4.1830091786095126E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.9150222634692798E-2</v>
+        <v>2.93401903777054E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7799954141538918E-2</v>
+        <v>2.7981122382011871E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.733801538143669E-2</v>
+        <v>1.7451004695158413E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.297613991647324E-2</v>
+        <v>1.3060703524917672E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.3989808512294527E-3</v>
+        <v>6.4406820747543187E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.1466881184386338E-3</v>
+        <v>4.1737114792104813E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.182923805593347E-2</v>
+        <v>7.2297338708432801E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2328100907526958E-2</v>
+        <v>8.2864621115688361E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5435520237114302E-2</v>
+        <v>5.5796785425176396E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8998670572398322E-2</v>
+        <v>3.9252819212083616E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9283953357599063E-2</v>
+        <v>2.9474792604199145E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0604144704569416E-2</v>
+        <v>3.0803587445340768E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1185310680097463E-2</v>
+        <v>2.1323372255316077E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2484744792514241E-2</v>
+        <v>1.2566106050712648E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7156268981343461E-3</v>
+        <v>7.7659085116278063E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5447190956628336E-3</v>
+        <v>5.5808532201064793E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-44.79</v>
+        <v>-44.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>44.79</v>
+        <v>44.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>44.79</v>
+        <v>44.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15038493389693097</v>
+        <v>0.15292578874872031</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742B2030-A885-4BAD-8D97-572B1D1F3107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0022DE-3464-44AB-8E82-81D0FA67FB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>44.5</v>
+        <v>45.61</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22532.480615500001</v>
+        <v>23094.526761189998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15292578874872031</v>
+        <v>0.14331902797975848</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.8606276641432779E-2</v>
+        <v>4.7423356951189627E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.247191011235955E-2</v>
+        <v>2.1925016443762334E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.247191011235955E-2</v>
+        <v>2.1925016443762334E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.247191011235955E-2</v>
+        <v>2.1925016443762334E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.247191011235955E-2</v>
+        <v>2.1925016443762334E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.1235955056179775E-2</v>
+        <v>1.0962508221881167E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8606276641432779E-2</v>
+        <v>4.7423356951189627E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.0477848239060337E-2</v>
+        <v>6.8762645179526086E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.0189252402585167E-2</v>
+        <v>6.8481072833041876E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.4597409677793243E-2</v>
+        <v>4.3512052853799596E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.1830091786095126E-2</v>
+        <v>4.0812082536312938E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.93401903777054E-2</v>
+        <v>2.8626144963996718E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7981122382011871E-2</v>
+        <v>2.7300152291153873E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.7451004695158413E-2</v>
+        <v>1.7026303638117725E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.3060703524917672E-2</v>
+        <v>1.2742848210016146E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.4406820747543187E-3</v>
+        <v>6.283936687712501E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.1737114792104813E-3</v>
+        <v>4.0721368301878183E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2297338708432801E-2</v>
+        <v>7.0537855131007673E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2864621115688361E-2</v>
+        <v>8.0847964035258332E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5796785425176396E-2</v>
+        <v>5.4438871989045158E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9252819212083616E-2</v>
+        <v>3.8297532447658864E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9474792604199145E-2</v>
+        <v>2.8757471407298004E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0803587445340768E-2</v>
+        <v>3.0053927676335544E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1323372255316077E-2</v>
+        <v>2.0804430286375037E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2566106050712648E-2</v>
+        <v>1.2260287639919159E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7659085116278063E-3</v>
+        <v>7.5769113959096119E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5808532201064793E-3</v>
+        <v>5.4450332886371048E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-44.5</v>
+        <v>-45.61</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>44.5</v>
+        <v>45.61</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>44.5</v>
+        <v>45.61</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15292578874872031</v>
+        <v>0.14331902797975848</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0022DE-3464-44AB-8E82-81D0FA67FB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A56D231-E14E-4517-AC33-71D9958DA57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.61</v>
+        <v>45.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23094.526761189998</v>
+        <v>23038.828494500001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14331902797975848</v>
+        <v>0.14425689465240721</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.7423356951189627E-2</v>
+        <v>4.7538006825137549E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.1925016443762334E-2</v>
+        <v>2.197802197802198E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.1925016443762334E-2</v>
+        <v>2.197802197802198E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1925016443762334E-2</v>
+        <v>2.197802197802198E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1925016443762334E-2</v>
+        <v>2.197802197802198E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.0962508221881167E-2</v>
+        <v>1.098901098901099E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7423356951189627E-2</v>
+        <v>4.7538006825137549E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8762645179526086E-2</v>
+        <v>6.8928884541498564E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8481072833041876E-2</v>
+        <v>6.8646631470660219E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.3512052853799596E-2</v>
+        <v>4.3617246827731854E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.0812082536312938E-2</v>
+        <v>4.0910749109477652E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.8626144963996718E-2</v>
+        <v>2.8695351028744844E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.7300152291153873E-2</v>
+        <v>2.736615265933029E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.7026303638117725E-2</v>
+        <v>1.7067466130429657E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2742848210016146E-2</v>
+        <v>1.2773655095798602E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.283936687712501E-3</v>
+        <v>6.2991286225619163E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.0721368301878183E-3</v>
+        <v>4.08198155659047E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0537855131007673E-2</v>
+        <v>7.0708386209346372E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0847964035258332E-2</v>
+        <v>8.1043420651607301E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4438871989045158E-2</v>
+        <v>5.457048244879889E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8297532447658864E-2</v>
+        <v>3.8390119888741116E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8757471407298004E-2</v>
+        <v>2.8826994964546417E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0053927676335544E-2</v>
+        <v>3.0126585523465147E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0804430286375037E-2</v>
+        <v>2.0854726711243197E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2260287639919159E-2</v>
+        <v>1.228992789575193E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5769113959096119E-3</v>
+        <v>7.5952292036799421E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4450332886371048E-3</v>
+        <v>5.4581971053788642E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.61</v>
+        <v>-45.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.61</v>
+        <v>45.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.61</v>
+        <v>45.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14331902797975848</v>
+        <v>0.14425689465240721</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A56D231-E14E-4517-AC33-71D9958DA57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AB7395-84B0-4C7F-A365-C512EA01ADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.5</v>
+        <v>45.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23038.828494500001</v>
+        <v>23281.875476419998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14425689465240721</v>
+        <v>0.14018665927281626</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.7538006825137549E-2</v>
+        <v>4.7041742291077833E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.197802197802198E-2</v>
+        <v>2.1748586341887779E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13495,20 +13495,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.197802197802198E-2</v>
+        <v>2.1748586341887779E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.197802197802198E-2</v>
+        <v>2.1748586341887779E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.197802197802198E-2</v>
+        <v>2.1748586341887779E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.098901098901099E-2</v>
+        <v>1.0874293170943889E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14694,50 +14694,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7538006825137549E-2</v>
+        <v>4.7041742291077833E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8928884541498564E-2</v>
+        <v>6.8209313758986187E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8646631470660219E-2</v>
+        <v>6.793000721868292E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.3617246827731854E-2</v>
+        <v>4.3161912367590247E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>4.0910749109477652E-2</v>
+        <v>4.0483668649004642E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.8695351028744844E-2</v>
+        <v>2.8395791035404315E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.736615265933029E-2</v>
+        <v>2.7080468595031063E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.7067466130429657E-2</v>
+        <v>1.6889293365257709E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2773655095798602E-2</v>
+        <v>1.2640306804237417E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2991286225619163E-3</v>
+        <v>6.2333699940532233E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.08198155659047E-3</v>
+        <v>4.0393684389923102E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14751,43 +14751,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0708386209346372E-2</v>
+        <v>6.9970238636913012E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1043420651607301E-2</v>
+        <v>8.0197382332495265E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.457048244879889E-2</v>
+        <v>5.4000803641155934E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8390119888741116E-2</v>
+        <v>3.7989353086944781E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8826994964546417E-2</v>
+        <v>2.8526060697843889E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0126585523465147E-2</v>
+        <v>2.9812084413172343E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0854726711243197E-2</v>
+        <v>2.0637017515475541E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.228992789575193E-2</v>
+        <v>1.2161629387923291E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5952292036799421E-3</v>
+        <v>7.5159401645810654E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4581971053788642E-3</v>
+        <v>5.4012172312905256E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.5</v>
+        <v>-45.98</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.5</v>
+        <v>45.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.5</v>
+        <v>45.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14425689465240721</v>
+        <v>0.14018665927281626</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AB7395-84B0-4C7F-A365-C512EA01ADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D80A37A-E607-4D6F-8A11-587CB03F7BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4477,11 +4479,11 @@
         <v>64.714648137522119</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14018665927281626</v>
+        <v>0.13823274619149584</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4490,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4501,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4509,37 +4511,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>28.803263731047231</v>
+        <v>28.630686160261423</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>40.844732114544499</v>
+        <v>40.629719578204039</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4547,18 +4549,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>57.008678420375631</v>
+        <v>56.741377225429467</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4566,18 +4568,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>52.931363368704652</v>
+        <v>52.676874362859721</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4589,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4597,45 +4599,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4650,18 +4652,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4686,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4708,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4733,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4748,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4761,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4778,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4800,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4821,27 +4823,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4854,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4867,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>4.7041742291077833E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>2.1748586341887779E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>1.9573727707699003E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4893,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.14549955248916155</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.18902580584937359</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.22405670341828193</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.24330033263324671</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.42456310191863128</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.50794527810050039</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.5295422156001708</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.5295422156001706</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4970,33 +4972,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5026,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5058,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5071,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5083,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5125,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5147,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5156,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5174,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5187,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5200,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5229,18 +5231,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5253,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5266,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5274,30 +5276,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5412,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5423,18 +5425,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5443,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5476,20 +5478,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5498,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5511,11 +5513,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7257757078580573</v>
+        <v>1.5531981370722512</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5540,11 +5542,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>28.803263731047231</v>
+        <v>28.630686160261423</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5553,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5566,21 +5568,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55491894710083656</v>
+        <v>0.55758569374556943</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.1501253634045896</v>
+        <v>1.9351128270641307</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5609,11 +5611,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>40.844732114544499</v>
+        <v>40.629719578204039</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5622,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5635,21 +5637,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.36884873378671179</v>
+        <v>0.37217120470370646</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5663,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.6730119494616398</v>
+        <v>2.4057107545154754</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5678,11 +5680,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>57.008678420375631</v>
+        <v>56.741377225429467</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5691,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5704,21 +5706,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.11907612787712119</v>
+        <v>0.12320658678617891</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>2.5448900584493499</v>
+        <v>2.2904010526044152</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5747,11 +5749,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>52.931363368704652</v>
+        <v>52.676874362859721</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5760,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5773,16 +5775,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.18057341576207186</v>
+        <v>0.18451314154115339</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5791,98 +5793,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5922,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5944,12 +5946,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6201,7 +6203,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351">
         <v>-70283969</v>
@@ -6237,7 +6239,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6253,7 +6255,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6505,7 +6507,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>1916547999</v>
@@ -6541,7 +6543,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-178527168</v>
@@ -6577,7 +6579,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-996799146</v>
@@ -6642,7 +6644,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6795,7 +6797,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7196,7 +7198,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7245,7 +7247,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7593,12 +7595,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7647,7 +7649,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7696,7 +7698,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7745,7 +7747,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7947,7 +7949,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8199,7 +8201,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8565,15 +8567,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8594,7 +8596,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8605,19 +8607,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8678,7 +8680,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8699,7 +8701,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>208734591.13999999</v>
@@ -8710,7 +8712,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8720,7 +8722,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8741,7 +8743,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8806,19 +8808,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8826,7 +8828,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>1017151265.9299999</v>
@@ -8855,7 +8857,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>40867997.270000003</v>
@@ -8875,7 +8877,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8886,7 +8888,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8895,7 +8897,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8916,7 +8918,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8936,7 +8938,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8956,7 +8958,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9016,16 +9018,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9058,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>2901653.62</v>
@@ -9102,7 +9104,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9152,10 +9154,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9163,10 +9165,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9188,7 +9190,7 @@
         <v>378055365.97000003</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9204,7 +9206,7 @@
         <v>44355236.240000002</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9220,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9249,14 +9251,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>422410602.21000004</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9276,7 +9278,7 @@
         <v>370532416.04999995</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9295,7 +9297,7 @@
         <v>792943018.25999999</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9319,13 +9321,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9333,7 +9335,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9365,7 +9367,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9392,7 +9394,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9406,7 +9408,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9418,7 +9420,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9432,7 +9434,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9449,7 +9451,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9486,10 +9488,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9498,7 +9500,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9509,12 +9511,12 @@
         <v>2.8914480193462864E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9525,13 +9527,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9539,7 +9541,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9550,12 +9552,12 @@
         <v>4150855827.3182759</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9565,7 +9567,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9575,7 +9577,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9585,7 +9587,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9598,7 +9600,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9610,7 +9612,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9621,12 +9623,12 @@
         <v>-463580763.570862</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9637,12 +9639,12 @@
         <v>10.953900061221555</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9650,12 +9652,12 @@
         <v>927161527.14172399</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9663,7 +9665,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9671,10 +9673,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9683,7 +9685,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9697,7 +9699,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9711,7 +9713,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9725,7 +9727,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9739,7 +9741,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9750,15 +9752,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9775,7 +9777,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9792,7 +9794,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9809,7 +9811,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9837,17 +9839,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10169,7 +10171,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10336,7 +10338,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10448,7 +10450,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10558,7 +10560,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10615,7 +10617,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10680,7 +10682,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10705,7 +10707,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10799,7 +10801,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -11018,7 +11020,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -11033,7 +11035,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11093,7 +11095,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11210,14 +11212,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-224833898</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11275,7 +11277,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11387,7 +11389,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11569,21 +11571,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11637,7 +11639,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11722,7 +11724,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11777,7 +11779,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11893,11 +11895,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11909,7 +11911,7 @@
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11936,7 +11938,7 @@
         <v>2.0195487899013917E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11985,7 +11987,7 @@
       </c>
       <c r="L55" s="42">
         <f t="shared" si="21"/>
-        <v>253.93107064861678</v>
+        <v>253.93107064861681</v>
       </c>
       <c r="M55" s="42">
         <f t="shared" si="21"/>
@@ -12015,17 +12017,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12080,7 +12082,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12135,7 +12137,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12190,7 +12192,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12245,13 +12247,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12301,7 +12303,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12360,17 +12362,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12395,7 +12397,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12420,7 +12422,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12445,7 +12447,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12475,12 +12477,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12498,7 +12500,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12690,7 +12692,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12863,7 +12865,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12977,7 +12979,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13149,7 +13151,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13256,7 +13258,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13317,7 +13319,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13436,7 +13438,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13491,1310 +13493,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>2.1748586341887779E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.1748586341887779E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>1.9573727707699003E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>1.9573727707699003E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.1748586341887779E-2</v>
-      </c>
-      <c r="I93" s="23">
+        <v>1.9573727707699003E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0874293170943889E-2</v>
-      </c>
-      <c r="J93" s="23">
+        <v>9.7868638538495013E-3</v>
+      </c>
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-0.16415582500084058</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>0.23557646468460058</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.15918951688273086</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.10241026278459486</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.67051733030020255</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.2374711605315063</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.39929822681154925</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.49891375301179886</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.63992176563831493</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.44976663618867407</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.23026619653665814</v>
+        <f>C4/G4-1</f>
+        <v>-0.16415582500084058</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>0.23557646468460058</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.15918951688273086</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.10241026278459486</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.67051733030020255</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.2374711605315063</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.39929822681154925</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.49891375301179886</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.63992176563831493</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.44976663618867407</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-0.23026619653665814</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>4.7314676461081007E-3</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>0.56394443176499331</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.11896887143890322</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>0.40074551783668522</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>3.9288422640898935E-2</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.55120279364046643</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>0.38870125557836643</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>0.95148801992160514</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>0.52094354919340469</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>15353846792.640001</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>15353846792.639999</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>14207301142</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>11801808511</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>9574469630</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>5869032275</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>4859452594</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>3633584727</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>2778559461</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>1371292107</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>1094930435</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>2470363699.1300001</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>2391271680</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>2078427810</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>1620191874</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>635971724</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>797615199</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>2342136338.9299998</v>
+        <f>BS!C4</f>
+        <v>2470363699.1300001</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>2391271680</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>2078427810</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>1620191874</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>635971724</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>797615199</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>2342136338.9299998</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>1921374942</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>1795225840</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1387177645</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>941597028</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>460791109</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>5315649326.7300005</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>5315649326.7300005</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>5242067251</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>4736625835</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>3596300871</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>2124874675</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>1651958950</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>1032202540</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>576053698</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>285486746</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>172274845</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>10038197465.91</v>
+        <f>BS!G30</f>
+        <v>5315649326.7300005</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>5315649326.7300005</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>5242067251</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>4736625835</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>3596300871</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>2124874675</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>1651958950</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>1032202540</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>576053698</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>285486746</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>172274845</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>10038197465.91</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>10038197465.91</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>8965233891</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>7065182676</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>5978168759</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>3744157600</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>3207493644</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>2601382187</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>2202505763</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>1085805361</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>922655590</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.37896704608794446</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.30661598351243974</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.32928385830346607</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.29754755893910678</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.12875704367393292</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.26976002687148287</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.35929628103429567</v>
+        <v>0.37896704608794446</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.24636442294063671</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>0.30661598351243974</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.28441636908297568</v>
+        <f t="shared" si="43"/>
+        <v>0.32928385830346607</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.25475459339617007</v>
+        <f t="shared" si="43"/>
+        <v>0.29754755893910678</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.19063308175858687</v>
+        <f t="shared" si="43"/>
+        <v>0.12875704367393292</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.15584334664362431</v>
+        <f t="shared" si="43"/>
+        <v>0.26976002687148287</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>0.35929628103429567</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.24636442294063671</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.28441636908297568</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.25475459339617007</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.19063308175858687</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.15584334664362431</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.1764903878265465</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>1.1929424225274436</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>0.74504662310350667</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0.42247280110140634</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>1.3427358596861791</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.0029926021469444</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>0.86522666985733043</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>1.2315448117899197</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>0.81345588557632331</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>0.89351097201094287</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.1764903878265465</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>1.1929424225274436</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>0.74504662310350667</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0.42247280110140634</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>1.3427358596861791</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.0029926021469444</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>0.86522666985733043</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>1.2315448117899197</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>0.81345588557632331</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>0.89351097201094287</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.2068632369052781</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.408374052605341</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.93214397117235537</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.39644303360502192</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.3488958482199989</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.1041647974466222</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.0572199531706012</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.1849072817273547</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.98083151944305158</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.1947528261563065</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.22405670341828193</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.24330033263324671</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.29920050733143649</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.2217662498105383</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.21848453158130443</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.26056281584450142</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.31024974693272739</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.27986793379403829</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.30207929409278672</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.25385060234769941</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.24197093577553586</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.42456310191863128</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.50794527810050039</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.44427606530704167</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.46138289974157676</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.51588403074813449</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.50378974990387149</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.49169227907483937</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.46993215578869862</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.40999080350434869</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.50657144342478155</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.43760880480046205</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.5295422156001708</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.5295422156001706</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.5847105959234813</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.6704180277022465</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.6015723235624368</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.5675174236789606</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.51503109073659</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.3967900392177168</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.2615446949911113</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.2629262630800364</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.1867163076527829</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.14549955248916155</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.18902580584937359</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.21065181445779718</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.17091576176343842</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.18051751009707057</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.20576625004800189</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.23111406161608458</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.18370434740531896</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.15624197302043563</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.16240406552938358</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.12565974265652041</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.1629793105437587</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.1362642466381847</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>3.1234217319150401</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.9845847306617994</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.8614390844812332</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.3056384718078904</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.2451599459995282</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.77656970893454935</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.58120130685883642</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.28661035232656717</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.1857301608248664</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7041742291077833E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>2.1629793105437587</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>3.1362642466381847</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>3.1234217319150401</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.9845847306617994</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.8614390844812332</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.3056384718078904</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.2451599459995282</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.77656970893454935</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.58120130685883642</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.28661035232656717</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.1857301608248664</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>4.7041742291077833E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>6.8209313758986187E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>6.793000721868292E-2</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>4.3161912367590247E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>4.0483668649004642E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>2.8395791035404315E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>2.7080468595031063E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>1.6889293365257709E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>1.2640306804237417E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>6.2333699940532233E-3</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>4.0393684389923102E-3</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.9970238636913012E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.0197382332495265E-2</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.4000803641155934E-2</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.7989353086944781E-2</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.8526060697843889E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.9812084413172343E-2</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.0637017515475541E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.2161629387923291E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>7.5159401645810654E-3</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.4012172312905256E-3</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15476,6 +15498,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15497,13 +15520,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15520,20 +15543,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15544,7 +15567,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15554,7 +15577,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15563,9 +15586,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15575,15 +15598,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15593,13 +15616,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15609,13 +15632,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15625,13 +15648,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15645,7 +15668,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15676,7 +15699,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15686,13 +15709,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15700,9 +15723,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15710,7 +15733,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15735,7 +15758,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16507,7 +16530,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16544,7 +16567,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16765,7 +16788,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16994,19 +17017,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17131,7 +17154,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17257,18 +17280,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17280,31 +17303,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>506347879</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>455713091.10000002</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17314,7 +17337,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17323,29 +17346,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>8439131316.666667</v>
+        <v>7595218185.000001</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>16.666666666666668</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17358,7 +17381,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17368,13 +17391,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17382,9 +17405,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17392,13 +17415,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>26.446957814887984</v>
+        <v>23.802262033399185</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17414,16 +17437,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17433,7 +17456,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>527872887.63928026</v>
+        <v>475085598.87535226</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17445,7 +17468,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>497993290.22573602</v>
+        <v>448193961.20316249</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17455,7 +17478,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>550312931.21034718</v>
+        <v>495281638.08931249</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17467,7 +17490,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>489776549.67101026</v>
+        <v>440798894.70390928</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17477,7 +17500,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>573706908.13783884</v>
+        <v>516336217.32405502</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17489,7 +17512,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>481695382.88137078</v>
+        <v>433525844.59323376</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17499,7 +17522,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>598095370.43073952</v>
+        <v>538285833.38766563</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17511,7 +17534,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>473747552.93018526</v>
+        <v>426372797.6371668</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17521,7 +17544,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>623520593.97677362</v>
+        <v>561168534.5790962</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17533,7 +17556,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>465930859.79944235</v>
+        <v>419337773.81949806</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17543,7 +17566,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>650026651.82503641</v>
+        <v>585023986.64253283</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -17555,7 +17578,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>458243139.77077097</v>
+        <v>412418825.7936939</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17565,7 +17588,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>677659490.58389366</v>
+        <v>609893541.52550435</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -17577,7 +17600,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>450682264.82650691</v>
+        <v>405614038.34385622</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17587,7 +17610,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>706467010.06657827</v>
+        <v>635820309.05992043</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -17599,7 +17622,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>443246142.06064188</v>
+        <v>398921527.85457766</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17609,7 +17632,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>736499146.32254863</v>
+        <v>662849231.69029379</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -17621,7 +17644,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>435932713.09949154</v>
+        <v>392339441.78954244</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17631,7 +17654,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>767807958.19853437</v>
+        <v>691027162.37868094</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -17643,7 +17666,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>428739953.53192276</v>
+        <v>385865958.17873049</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -17653,7 +17676,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>800447717.57932067</v>
+        <v>720402945.82138872</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -17665,7 +17688,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>421665872.34898108</v>
+        <v>379499285.11408305</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -17675,7 +17698,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>834475003.46469724</v>
+        <v>751027503.1182276</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -17687,7 +17710,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>414708511.39276588</v>
+        <v>373237660.25348932</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -17697,7 +17720,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>869948800.04564643</v>
+        <v>782953920.04108179</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -17709,7 +17732,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>407865944.81439638</v>
+        <v>367079350.33295673</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -17719,7 +17742,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>906930598.94978273</v>
+        <v>816237539.05480456</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -17731,7 +17754,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>401136278.5409233</v>
+        <v>361022650.686831</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -17741,7 +17764,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>945484505.83327878</v>
+        <v>850936055.249951</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -17753,7 +17776,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>394517649.75103545</v>
+        <v>355065884.77593195</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -17763,7 +17786,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>985677351.50404525</v>
+        <v>887109616.35364079</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -17775,7 +17798,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>388008226.35941708</v>
+        <v>349207403.7234754</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -17785,7 +17808,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>1027578807.7687953</v>
+        <v>924820926.99191582</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -17797,7 +17820,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>381606206.50961244</v>
+        <v>343445585.85865122</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17807,7 +17830,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>1071261508.2048025</v>
+        <v>964135357.38432229</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -17819,7 +17842,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>375309818.07525975</v>
+        <v>337778836.26773375</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -17829,7 +17852,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>1116801174.0657051</v>
+        <v>1005121056.6591346</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -17841,7 +17864,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>369117318.16955233</v>
+        <v>332205586.35259712</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -17851,7 +17874,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>1164276745.5396061</v>
+        <v>1047849070.9856454</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -17863,7 +17886,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>363026992.66279596</v>
+        <v>326724293.39651632</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -17873,7 +17896,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>1213770518.5869956</v>
+        <v>1092393466.728296</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
@@ -17885,7 +17908,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>357037155.70792353</v>
+        <v>321333440.13713121</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17895,7 +17918,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>1265368287.5956986</v>
+        <v>1138831458.8361287</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
@@ -17907,7 +17930,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>351146149.27384192</v>
+        <v>316031534.34645772</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17917,7 +17940,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>1319159494.1001277</v>
+        <v>1187243544.690115</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
@@ -17929,7 +17952,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>345352342.68647546</v>
+        <v>310817108.41782796</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17939,7 +17962,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>1375237381.8226392</v>
+        <v>1237713643.6403754</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
@@ -17951,7 +17974,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>339654132.17738366</v>
+        <v>305688718.95964533</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17961,7 +17984,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>1433699158.3057463</v>
+        <v>1290329242.4751718</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
@@ -17973,7 +17996,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>334049940.43982619</v>
+        <v>300644946.39584363</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17983,7 +18006,7 @@
       </c>
       <c r="C41" s="123">
         <f t="shared" si="2"/>
-        <v>1494646163.41537</v>
+        <v>1345181547.073833</v>
       </c>
       <c r="D41" s="138">
         <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
@@ -17995,7 +18018,7 @@
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>328538216.19215322</v>
+        <v>295684394.57293791</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -18005,7 +18028,7 @@
       </c>
       <c r="C42" s="123">
         <f t="shared" si="2"/>
-        <v>1558184045.0072131</v>
+        <v>1402365640.5064919</v>
       </c>
       <c r="D42" s="138">
         <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
@@ -18017,7 +18040,7 @@
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>323117433.74839842</v>
+        <v>290805690.37355858</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -18027,7 +18050,7 @@
       </c>
       <c r="C43" s="123">
         <f t="shared" si="2"/>
-        <v>1624422942.0607719</v>
+        <v>1461980647.8546948</v>
       </c>
       <c r="D43" s="138">
         <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
@@ -18039,7 +18062,7 @@
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>317786092.59595853</v>
+        <v>286007483.33636272</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -18049,7 +18072,7 @@
       </c>
       <c r="C44" s="123">
         <f t="shared" si="2"/>
-        <v>1693477675.5984297</v>
+        <v>1524129908.0385869</v>
       </c>
       <c r="D44" s="138">
         <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
@@ -18061,7 +18084,7 @@
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>312542716.98023999</v>
+        <v>281288445.28221601</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -18071,7 +18094,7 @@
       </c>
       <c r="C45" s="123">
         <f t="shared" si="2"/>
-        <v>1765467947.7205813</v>
+        <v>1588921152.948523</v>
       </c>
       <c r="D45" s="138">
         <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
@@ -18083,17 +18106,17 @@
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>307385855.4961592</v>
+        <v>276647269.94654328</v>
       </c>
       <c r="H45" s="120"/>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>8797881460.6546707</v>
+        <v>7918093314.5892048</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18105,7 +18128,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>1531800292.850827</v>
+        <v>1378620263.5657444</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18116,7 +18139,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>13391360995.571005</v>
+        <v>12052224896.013905</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18126,7 +18149,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18137,7 +18160,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>13391360995.571005</v>
+        <v>12052224896.013905</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18167,19 +18190,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>8439131316.6666641</v>
+        <v>7595218184.9999981</v>
       </c>
       <c r="C51" s="123">
-        <v>8691480151.0647202</v>
+        <v>7822332135.9582491</v>
       </c>
       <c r="D51" s="123">
-        <v>8950446183.2749805</v>
+        <v>8055401564.9474831</v>
       </c>
       <c r="E51" s="123">
-        <v>9216321834.1651993</v>
+        <v>8294689650.7486792</v>
       </c>
       <c r="F51" s="123">
-        <v>9489408620.0748119</v>
+        <v>8540467758.0673313</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18188,19 +18211,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>8439131316.6666622</v>
+        <v>7595218184.9999981</v>
       </c>
       <c r="C52" s="123">
-        <v>8929631292.8753948</v>
+        <v>8036668163.5878563</v>
       </c>
       <c r="D52" s="123">
-        <v>9467534449.6062794</v>
+        <v>8520781004.6456509</v>
       </c>
       <c r="E52" s="123">
-        <v>10058587649.863117</v>
+        <v>9052728884.8768044</v>
       </c>
       <c r="F52" s="123">
-        <v>10709185671.001583</v>
+        <v>9638267103.9014263</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18209,19 +18232,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>8439131316.6666613</v>
+        <v>7595218184.9999962</v>
       </c>
       <c r="C53" s="123">
-        <v>9252554677.3211136</v>
+        <v>8327299209.5890017</v>
       </c>
       <c r="D53" s="123">
-        <v>10206004926.347317</v>
+        <v>9185404433.7125854</v>
       </c>
       <c r="E53" s="123">
-        <v>11327854104.888365</v>
+        <v>10195068694.39953</v>
       </c>
       <c r="F53" s="123">
-        <v>12652154631.583279</v>
+        <v>11386939168.424952</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18230,19 +18253,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>8439131316.6666622</v>
+        <v>7595218184.9999962</v>
       </c>
       <c r="C54" s="123">
-        <v>9613461130.6716042</v>
+        <v>8652115017.6044426</v>
       </c>
       <c r="D54" s="123">
-        <v>11077920670.606377</v>
+        <v>9970128603.5457382</v>
       </c>
       <c r="E54" s="123">
-        <v>12916200277.469994</v>
+        <v>11624580249.723</v>
       </c>
       <c r="F54" s="123">
-        <v>15236586143.229223</v>
+        <v>13712927528.906301</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18251,19 +18274,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>8439131316.6666613</v>
+        <v>7595218184.9999952</v>
       </c>
       <c r="C55" s="123">
-        <v>9981824857.6059265</v>
+        <v>8983642371.8453331</v>
       </c>
       <c r="D55" s="123">
-        <v>12020475743.382088</v>
+        <v>10818428169.043877</v>
       </c>
       <c r="E55" s="123">
-        <v>14742981376.79142</v>
+        <v>13268683239.112284</v>
       </c>
       <c r="F55" s="123">
-        <v>18411307027.537109</v>
+        <v>16570176324.783398</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18272,19 +18295,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>8439131316.6666603</v>
+        <v>7595218184.9999943</v>
       </c>
       <c r="C56" s="123">
-        <v>10338496538.975384</v>
+        <v>9304646885.0778427</v>
       </c>
       <c r="D56" s="123">
-        <v>12989379585.600565</v>
+        <v>11690441627.040508</v>
       </c>
       <c r="E56" s="123">
-        <v>16747934923.81588</v>
+        <v>15073141431.434299</v>
       </c>
       <c r="F56" s="123">
-        <v>22148947314.659946</v>
+        <v>19934052583.193951</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18297,7 +18320,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18334,23 +18357,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>16.666666666666668</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>16.666666666666668</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>16.666666666666668</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>16.666666666666668</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>16.666666666666668</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18361,23 +18384,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>16.666666666666661</v>
+        <v>14.999999999999996</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>17.165037144482085</v>
+        <v>15.448533430033878</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>17.676476103645296</v>
+        <v>15.908828493280769</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>18.201561053967009</v>
+        <v>16.381404948570307</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>18.740887468148774</v>
+        <v>16.866798721333897</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18388,23 +18411,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>16.666666666666657</v>
+        <v>14.999999999999996</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>17.63536821860647</v>
+        <v>15.871831396745826</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>18.697687582505463</v>
+        <v>16.827918824254915</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>19.864974392167085</v>
+        <v>17.878476952950372</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>21.149857864817051</v>
+        <v>19.034872078335351</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18415,23 +18438,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>16.666666666666657</v>
+        <v>14.999999999999993</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>18.273118267216269</v>
+        <v>16.445806440494643</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>20.15611272333841</v>
+        <v>18.140501451004567</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>22.371682739661214</v>
+        <v>20.134514465695098</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>24.987079350604485</v>
+        <v>22.488371415544037</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18442,23 +18465,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>16.666666666666657</v>
+        <v>14.999999999999993</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>18.985882096825382</v>
+        <v>17.087293887142842</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>21.8780825002851</v>
+        <v>19.690274250256586</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>25.508550174987487</v>
+        <v>22.95769515748875</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>30.091142424296052</v>
+        <v>27.082028181866448</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18469,23 +18492,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>16.666666666666657</v>
+        <v>14.999999999999991</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>19.713373495943738</v>
+        <v>17.742036146349363</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>23.739559780761098</v>
+        <v>21.365603802684983</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>29.11630913890215</v>
+        <v>26.204678225011946</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>36.360983804056005</v>
+        <v>32.724885423650406</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18495,40 +18518,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>16.666666666666654</v>
+        <v>14.999999999999989</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.417773960845174</v>
+        <v>18.375996564760651</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>25.653073952346041</v>
+        <v>23.087766557111436</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.075945646087874</v>
+        <v>29.768351081479103</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>43.742549802721591</v>
+        <v>39.368294822449428</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18546,7 +18569,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>43.742549802721591</v>
+        <v>39.368294822449428</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18568,7 +18591,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>33.075945646087874</v>
+        <v>29.768351081479103</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18591,7 +18614,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>25.653073952346041</v>
+        <v>23.087766557111436</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18614,7 +18637,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>20.417773960845174</v>
+        <v>18.375996564760651</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18637,7 +18660,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>16.666666666666654</v>
+        <v>14.999999999999989</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18653,7 +18676,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18705,32 +18728,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18742,14 +18765,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18757,7 +18780,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18766,7 +18789,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18778,7 +18801,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18786,12 +18809,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>65.714648137522119</v>
+        <v>65.614648137522124</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18801,11 +18824,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 浙江鼎力(603338.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18826,8 +18849,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18848,8 +18871,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18859,8 +18882,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18871,10 +18894,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18885,15 +18908,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.16445427582528804</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18904,14 +18927,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.21768298308972489</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18928,12 +18951,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.18992961357468019</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18942,38 +18965,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18983,12 +19006,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18998,44 +19021,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19045,55 +19068,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19103,55 +19126,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19161,24 +19184,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19191,7 +19214,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19200,12 +19223,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>30</v>
@@ -19220,39 +19243,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19262,55 +19285,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19320,23 +19343,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19347,7 +19370,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19356,7 +19379,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19365,15 +19388,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19381,19 +19404,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>4.25103165866728E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19409,20 +19432,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19432,19 +19455,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19454,14 +19477,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19470,7 +19493,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19479,12 +19502,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19494,11 +19517,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>1</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.9</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19507,25 +19530,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.7257757078580573</v>
+        <v>1.5531981370722512</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19533,7 +19556,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19547,18 +19570,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>28.803263731047231</v>
+        <v>28.630686160261423</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.55491894710083656</v>
+        <v>0.55758569374556943</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19566,12 +19589,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19584,11 +19607,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14018665927281626</v>
+        <v>0.13823274619149584</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19596,12 +19619,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19610,11 +19633,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.1501253634045896</v>
+        <v>1.9351128270641307</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19622,7 +19645,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19636,30 +19659,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>40.844732114544499</v>
+        <v>40.629719578204039</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.36884873378671179</v>
+        <v>0.37217120470370646</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19670,11 +19693,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.6730119494616398</v>
+        <v>2.4057107545154754</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19682,7 +19705,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19694,21 +19717,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>57.008678420375631</v>
+        <v>56.741377225429467</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.11907612787712119</v>
+        <v>0.12320658678617891</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19716,12 +19739,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19730,17 +19753,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.5448900584493499</v>
+        <v>2.2904010526044152</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19750,21 +19773,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>52.931363368704652</v>
+        <v>52.676874362859721</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.18057341576207186</v>
+        <v>0.18451314154115339</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19772,32 +19795,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D80A37A-E607-4D6F-8A11-587CB03F7BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53371B6C-12B3-41F6-B9AA-F65C66131FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.98</v>
+        <v>46.46</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23281.875476419998</v>
+        <v>23524.922458339999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13823274619149584</v>
+        <v>0.13423361415165758</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.7041742291077833E-2</v>
+        <v>4.655573203925438E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9573727707699003E-2</v>
+        <v>1.9371502367628066E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.5531981370722512</v>
+        <v>1.5531981370722516</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9573727707699003E-2</v>
+        <v>1.9371502367628066E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9573727707699003E-2</v>
+        <v>1.9371502367628066E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9573727707699003E-2</v>
+        <v>1.9371502367628066E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.7868638538495013E-3</v>
+        <v>9.6857511838140328E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7041742291077833E-2</v>
+        <v>4.655573203925438E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.8209313758986187E-2</v>
+        <v>6.7504611421398727E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.793000721868292E-2</v>
+        <v>6.7228190527659062E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.3161912367590247E-2</v>
+        <v>4.2715986454192841E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.0483668649004642E-2</v>
+        <v>4.0065412924692921E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8395791035404315E-2</v>
+        <v>2.8102420830992045E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.7080468595031063E-2</v>
+        <v>2.680068760222833E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6889293365257709E-2</v>
+        <v>1.6714802172504289E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2640306804237417E-2</v>
+        <v>1.250971387987164E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.2333699940532233E-3</v>
+        <v>6.1689701318675674E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.0393684389923102E-3</v>
+        <v>3.9976358335098239E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9970238636913012E-2</v>
+        <v>6.9247343360423153E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0197382332495265E-2</v>
+        <v>7.9368825648905128E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4000803641155934E-2</v>
+        <v>5.3442896070175411E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7989353086944781E-2</v>
+        <v>3.7596867303868291E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8526060697843889E-2</v>
+        <v>2.823134461659195E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9812084413172343E-2</v>
+        <v>2.9504081819149035E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0637017515475541E-2</v>
+        <v>2.0423806830855904E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2161629387923291E-2</v>
+        <v>1.2035981903932692E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5159401645810654E-3</v>
+        <v>7.4382894698113945E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4012172312905256E-3</v>
+        <v>5.3454147286857148E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.98</v>
+        <v>-46.46</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.98</v>
+        <v>46.46</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5531981370722512</v>
+        <v>1.5531981370722516</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.98</v>
+        <v>46.46</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13823274619149584</v>
+        <v>0.13423361415165758</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53371B6C-12B3-41F6-B9AA-F65C66131FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD677ED-28CB-407C-AFC0-728F34D02F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>46.46</v>
+        <v>44.81</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23524.922458339999</v>
+        <v>22689.448457990002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13423361415165758</v>
+        <v>0.14822098134465111</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.655573203925438E-2</v>
+        <v>4.8270013625167564E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9371502367628066E-2</v>
+        <v>2.0084802499442087E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9371502367628066E-2</v>
+        <v>2.0084802499442087E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9371502367628066E-2</v>
+        <v>2.0084802499442087E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9371502367628066E-2</v>
+        <v>2.0084802499442087E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6857511838140328E-3</v>
+        <v>1.0042401249721044E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.655573203925438E-2</v>
+        <v>4.8270013625167564E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.7504611421398727E-2</v>
+        <v>6.9990275533099416E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.7228190527659062E-2</v>
+        <v>6.9703676231087697E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2715986454192841E-2</v>
+        <v>4.4288880398611903E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.0065412924692921E-2</v>
+        <v>4.1540707085053183E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8102420830992045E-2</v>
+        <v>2.9137212046594294E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.680068760222833E-2</v>
+        <v>2.7787546217351664E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6714802172504289E-2</v>
+        <v>1.7330276923332947E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.250971387987164E-2</v>
+        <v>1.2970348289641517E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.1689701318675674E-3</v>
+        <v>6.396124800860682E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.9976358335098239E-3</v>
+        <v>4.1448373315078422E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9247343360423153E-2</v>
+        <v>7.1797178587932595E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9368825648905128E-2</v>
+        <v>8.2291355493151794E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3442896070175411E-2</v>
+        <v>5.5410777759882825E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7596867303868291E-2</v>
+        <v>3.8981264336927487E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.823134461659195E-2</v>
+        <v>2.9270883081608166E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9504081819149035E-2</v>
+        <v>3.0590485188968179E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0423806830855904E-2</v>
+        <v>2.1175855062744151E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2035981903932692E-2</v>
+        <v>1.2479172489549493E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4382894698113945E-3</v>
+        <v>7.7121831905252701E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3454147286857148E-3</v>
+        <v>5.5422443270416941E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.46</v>
+        <v>-44.81</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.46</v>
+        <v>44.81</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.46</v>
+        <v>44.81</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13423361415165758</v>
+        <v>0.14822098134465111</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD677ED-28CB-407C-AFC0-728F34D02F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E800119-33F3-4187-BFD5-7FC8C91B0B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>44.81</v>
+        <v>43.12</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22689.448457990002</v>
+        <v>21833.720542480001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14822098134465111</v>
+        <v>0.16328643894343076</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.8270013625167564E-2</v>
+        <v>5.0161857851200344E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.0084802499442087E-2</v>
+        <v>2.0871985157699446E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0084802499442087E-2</v>
+        <v>2.0871985157699446E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0084802499442087E-2</v>
+        <v>2.0871985157699446E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0084802499442087E-2</v>
+        <v>2.0871985157699446E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0042401249721044E-2</v>
+        <v>1.0435992578849723E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8270013625167564E-2</v>
+        <v>5.0161857851200344E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.9990275533099416E-2</v>
+        <v>7.2733400896061798E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.9703676231087697E-2</v>
+        <v>7.2435568921962901E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.4288880398611903E-2</v>
+        <v>4.6024692269522251E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.1540707085053183E-2</v>
+        <v>4.3168809936948827E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.9137212046594294E-2</v>
+        <v>3.0279185338772972E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.7787546217351664E-2</v>
+        <v>2.8876622124293327E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.7330276923332947E-2</v>
+        <v>1.8009501598667658E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2970348289641517E-2</v>
+        <v>1.3478694500436837E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.396124800860682E-3</v>
+        <v>6.6468077997812432E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.1448373315078422E-3</v>
+        <v>4.3072857334152696E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1797178587932595E-2</v>
+        <v>7.4611121811810288E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2291355493151794E-2</v>
+        <v>8.5516596466793424E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5410777759882825E-2</v>
+        <v>5.7582489596946881E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8981264336927487E-2</v>
+        <v>4.0509055077405397E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9270883081608166E-2</v>
+        <v>3.0418095335966188E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0590485188968179E-2</v>
+        <v>3.1789416542617445E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1175855062744151E-2</v>
+        <v>2.2005799289461163E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2479172489549493E-2</v>
+        <v>1.296826807181616E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7121831905252701E-3</v>
+        <v>8.014446399986953E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5422443270416941E-3</v>
+        <v>5.7594612313251001E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-44.81</v>
+        <v>-43.12</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>44.81</v>
+        <v>43.12</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>44.81</v>
+        <v>43.12</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14822098134465111</v>
+        <v>0.16328643894343076</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E800119-33F3-4187-BFD5-7FC8C91B0B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8425A9DF-32B1-4F52-B9BB-B83DD3DF07D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>43.12</v>
+        <v>42.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21833.720542480001</v>
+        <v>21626.117912090001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16328643894343076</v>
+        <v>0.16706180736987131</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0161857851200344E-2</v>
+        <v>5.06433928949604E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.0871985157699446E-2</v>
+        <v>2.1072348396160151E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0871985157699446E-2</v>
+        <v>2.1072348396160151E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0871985157699446E-2</v>
+        <v>2.1072348396160151E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0871985157699446E-2</v>
+        <v>2.1072348396160151E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0435992578849723E-2</v>
+        <v>1.0536174198080075E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0161857851200344E-2</v>
+        <v>5.06433928949604E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.2733400896061798E-2</v>
+        <v>7.3431614297311751E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>7.2435568921962901E-2</v>
+        <v>7.313092324783517E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.6024692269522251E-2</v>
+        <v>4.6466512073561214E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.3168809936948827E-2</v>
+        <v>4.3583214340464367E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.0279185338772972E-2</v>
+        <v>3.0569854174851096E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.8876622124293327E-2</v>
+        <v>2.9153826878940019E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.8009501598667658E-2</v>
+        <v>1.8182386067303893E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.3478694500436837E-2</v>
+        <v>1.3608084918258871E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.6468077997812432E-3</v>
+        <v>6.7106146646351483E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.3072857334152696E-3</v>
+        <v>4.3486340628627112E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4611121811810288E-2</v>
+        <v>7.5327360630420503E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5516596466793424E-2</v>
+        <v>8.6337523756687712E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7582489596946881E-2</v>
+        <v>5.8135259925552553E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0509055077405397E-2</v>
+        <v>4.0897926830665433E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0418095335966188E-2</v>
+        <v>3.0710097655978975E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1789416542617445E-2</v>
+        <v>3.2094583032490381E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2005799289461163E-2</v>
+        <v>2.2217046718837868E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.296826807181616E-2</v>
+        <v>1.3092758587139144E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.014446399986953E-3</v>
+        <v>8.0913820830587069E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7594612313251001E-3</v>
+        <v>5.8147499015391785E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-43.12</v>
+        <v>-42.71</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>43.12</v>
+        <v>42.71</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>43.12</v>
+        <v>42.71</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16328643894343076</v>
+        <v>0.16706180736987131</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8425A9DF-32B1-4F52-B9BB-B83DD3DF07D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2772359-BFC9-45DE-A50D-DCD8FDCEC4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>42.71</v>
+        <v>42.53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21626.117912090001</v>
+        <v>21534.97529387</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16706180736987131</v>
+        <v>0.16873476418140121</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.06433928949604E-2</v>
+        <v>5.085773126131575E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.1072348396160151E-2</v>
+        <v>2.1161533035504349E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1072348396160151E-2</v>
+        <v>2.1161533035504349E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1072348396160151E-2</v>
+        <v>2.1161533035504349E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.1072348396160151E-2</v>
+        <v>2.1161533035504349E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0536174198080075E-2</v>
+        <v>1.0580766517752175E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.06433928949604E-2</v>
+        <v>5.085773126131575E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.3431614297311751E-2</v>
+        <v>7.3742399403672346E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>7.313092324783517E-2</v>
+        <v>7.3440435737480367E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.6466512073561214E-2</v>
+        <v>4.6663172599619079E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.3583214340464367E-2</v>
+        <v>4.3767671866476211E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.0569854174851096E-2</v>
+        <v>3.0699235170653431E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.9153826878940019E-2</v>
+        <v>2.927721481306203E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.8182386067303893E-2</v>
+        <v>1.8259339499989403E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.3608084918258871E-2</v>
+        <v>1.3665678505968408E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.7106146646351483E-3</v>
+        <v>6.739016043417991E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.3486340628627112E-3</v>
+        <v>4.3670388155388293E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5327360630420503E-2</v>
+        <v>7.5646169116512105E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6337523756687712E-2</v>
+        <v>8.6702930628923869E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8135259925552553E-2</v>
+        <v>5.8381306170240996E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0897926830665433E-2</v>
+        <v>4.1071019396607594E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0710097655978975E-2</v>
+        <v>3.0840072205193088E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2094583032490381E-2</v>
+        <v>3.2230417148310937E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2217046718837868E-2</v>
+        <v>2.2311076072456276E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3092758587139144E-2</v>
+        <v>1.314817115581267E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0913820830587069E-3</v>
+        <v>8.1256272929094136E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8147499015391785E-3</v>
+        <v>5.839359705966103E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-42.71</v>
+        <v>-42.53</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>42.71</v>
+        <v>42.53</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>42.71</v>
+        <v>42.53</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16706180736987131</v>
+        <v>0.16873476418140121</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2772359-BFC9-45DE-A50D-DCD8FDCEC4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F26EFB-D469-4E6C-BFC9-43D8BFD8E268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>42.53</v>
+        <v>43.54</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>21534.97529387</v>
+        <v>22046.386651659999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16873476418140121</v>
+        <v>0.15946886660280679</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.085773126131575E-2</v>
+        <v>4.9677981408905801E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.1161533035504349E-2</v>
+        <v>2.0670647680293985E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1161533035504349E-2</v>
+        <v>2.0670647680293985E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1161533035504349E-2</v>
+        <v>2.0670647680293985E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.1161533035504349E-2</v>
+        <v>2.0670647680293985E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0580766517752175E-2</v>
+        <v>1.0335323840146992E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.085773126131575E-2</v>
+        <v>4.9677981408905801E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.3742399403672346E-2</v>
+        <v>7.2031792527289501E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>7.3440435737480367E-2</v>
+        <v>7.1736833530432711E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.6663172599619079E-2</v>
+        <v>4.55807241768902E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.3767671866476211E-2</v>
+        <v>4.2752390548489512E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>3.0699235170653431E-2</v>
+        <v>2.9987103165087056E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.927721481306203E-2</v>
+        <v>2.8598069499300143E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.8259339499989403E-2</v>
+        <v>1.7835776502860574E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.3665678505968408E-2</v>
+        <v>1.3348674939339377E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.739016043417991E-3</v>
+        <v>6.5826906827415521E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.3670388155388293E-3</v>
+        <v>4.2657363533501703E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5646169116512105E-2</v>
+        <v>7.3891400379542033E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6702930628923869E-2</v>
+        <v>8.4691677529814699E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8381306170240996E-2</v>
+        <v>5.7027031497940965E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1071019396607594E-2</v>
+        <v>4.0118292488234286E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0840072205193088E-2</v>
+        <v>3.0124673194461691E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2230417148310937E-2</v>
+        <v>3.1482766222270649E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2311076072456276E-2</v>
+        <v>2.1793524698244495E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.314817115581267E-2</v>
+        <v>1.2843172238325972E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1256272929094136E-3</v>
+        <v>7.9371366276398108E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.839359705966103E-3</v>
+        <v>5.7039037274859514E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-42.53</v>
+        <v>-43.54</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>42.53</v>
+        <v>43.54</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>42.53</v>
+        <v>43.54</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16873476418140121</v>
+        <v>0.15946886660280679</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F26EFB-D469-4E6C-BFC9-43D8BFD8E268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA420161-869F-48FA-A341-CC5A47D837EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>43.54</v>
+        <v>44.19</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22046.386651659999</v>
+        <v>22375.512773009999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15946886660280679</v>
+        <v>0.15365760495616176</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.9677981408905801E-2</v>
+        <v>4.8947257536631789E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.0670647680293985E-2</v>
+        <v>2.0366598778004074E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0670647680293985E-2</v>
+        <v>2.0366598778004074E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0670647680293985E-2</v>
+        <v>2.0366598778004074E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0670647680293985E-2</v>
+        <v>2.0366598778004074E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0335323840146992E-2</v>
+        <v>1.0183299389002037E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9677981408905801E-2</v>
+        <v>4.8947257536631789E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.2031792527289501E-2</v>
+        <v>7.0972261747865695E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>7.1736833530432711E-2</v>
+        <v>7.0681641364902473E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.55807241768902E-2</v>
+        <v>4.4910267722602384E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.2752390548489512E-2</v>
+        <v>4.2123536648138338E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.9987103165087056E-2</v>
+        <v>2.9546016560486318E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.8598069499300143E-2</v>
+        <v>2.817741448290401E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.7835776502860574E-2</v>
+        <v>1.7573426316690413E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.3348674939339377E-2</v>
+        <v>1.3152326473383944E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.5826906827415521E-3</v>
+        <v>6.4858645016195333E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.2657363533501703E-3</v>
+        <v>4.2029907405491378E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3891400379542033E-2</v>
+        <v>7.2804516237276767E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4691677529814699E-2</v>
+        <v>8.3445929840419375E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7027031497940965E-2</v>
+        <v>5.6188208902927125E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0118292488234286E-2</v>
+        <v>3.9528184090014053E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0124673194461691E-2</v>
+        <v>2.9681563043377733E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1482766222270649E-2</v>
+        <v>3.1019679595330713E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1793524698244495E-2</v>
+        <v>2.1472959161836738E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2843172238325972E-2</v>
+        <v>1.265425931787085E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9371366276398108E-3</v>
+        <v>7.8203876163710651E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7039037274859514E-3</v>
+        <v>5.6200038084349025E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-43.54</v>
+        <v>-44.19</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>43.54</v>
+        <v>44.19</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>43.54</v>
+        <v>44.19</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15946886660280679</v>
+        <v>0.15365760495616176</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA420161-869F-48FA-A341-CC5A47D837EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418C9A71-525A-428B-9F3C-B49160B0620D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>44.19</v>
+        <v>46.19</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>22375.512773009999</v>
+        <v>23388.208531009997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15365760495616176</v>
+        <v>0.13647623248050844</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.8947257536631789E-2</v>
+        <v>4.6827869897028765E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.0366598778004074E-2</v>
+        <v>1.9484736956051095E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0366598778004074E-2</v>
+        <v>1.9484736956051095E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0366598778004074E-2</v>
+        <v>1.9484736956051095E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0366598778004074E-2</v>
+        <v>1.9484736956051095E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.0183299389002037E-2</v>
+        <v>9.7423684780255475E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8947257536631789E-2</v>
+        <v>4.6827869897028765E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.0972261747865695E-2</v>
+        <v>6.7899204300458649E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>7.0681641364902473E-2</v>
+        <v>6.7621167610197888E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.4910267722602384E-2</v>
+        <v>4.2965679382156299E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.2123536648138338E-2</v>
+        <v>4.029961213425489E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.9546016560486318E-2</v>
+        <v>2.8266691314308087E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.817741448290401E-2</v>
+        <v>2.6957348906679546E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.7573426316690413E-2</v>
+        <v>1.6812507229585393E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.3152326473383944E-2</v>
+        <v>1.2582838425175069E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.4858645016195333E-3</v>
+        <v>6.2050303599603205E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.2029907405491378E-3</v>
+        <v>4.0210036983084306E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2804516237276767E-2</v>
+        <v>6.9652123241508115E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3445929840419375E-2</v>
+        <v>7.9832769855989014E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6188208902927125E-2</v>
+        <v>5.3755292301804494E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9528184090014053E-2</v>
+        <v>3.7816636824804524E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9681563043377733E-2</v>
+        <v>2.839636871372293E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1019679595330713E-2</v>
+        <v>2.9676545601161813E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1472959161836738E-2</v>
+        <v>2.0543192581978037E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.265425931787085E-2</v>
+        <v>1.2106337286354468E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8203876163710651E-3</v>
+        <v>7.4817694039280664E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6200038084349025E-3</v>
+        <v>5.3766609286585486E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-44.19</v>
+        <v>-46.19</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>44.19</v>
+        <v>46.19</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>44.19</v>
+        <v>46.19</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15365760495616176</v>
+        <v>0.13647623248050844</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418C9A71-525A-428B-9F3C-B49160B0620D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FF2405-5F61-43BD-9FA1-1DD6A618DBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>46.19</v>
+        <v>46.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23388.208531009997</v>
+        <v>23712.27117357</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13647623248050844</v>
+        <v>0.1311887749570162</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6827869897028765E-2</v>
+        <v>4.6187899007981183E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9484736956051095E-2</v>
+        <v>1.9218449711723255E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9484736956051095E-2</v>
+        <v>1.9218449711723255E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9484736956051095E-2</v>
+        <v>1.9218449711723255E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9484736956051095E-2</v>
+        <v>1.9218449711723255E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.7423684780255475E-3</v>
+        <v>9.6092248558616276E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6827869897028765E-2</v>
+        <v>4.6187899007981183E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.7899204300458649E-2</v>
+        <v>6.6971263007435083E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.7621167610197888E-2</v>
+        <v>6.6697026092569722E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2965679382156299E-2</v>
+        <v>4.2378490938752927E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.029961213425489E-2</v>
+        <v>3.9748859373931952E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8266691314308087E-2</v>
+        <v>2.7880385902367934E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6957348906679546E-2</v>
+        <v>2.6588937561382194E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6812507229585393E-2</v>
+        <v>1.6582739887562446E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2582838425175069E-2</v>
+        <v>1.2410875653615983E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.2050303599603205E-3</v>
+        <v>6.120229603386017E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.0210036983084306E-3</v>
+        <v>3.9660508397366305E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9652123241508115E-2</v>
+        <v>6.870022576393893E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9832769855989014E-2</v>
+        <v>7.8741739048646855E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3755292301804494E-2</v>
+        <v>5.3020648119161851E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7816636824804524E-2</v>
+        <v>3.7299817530167007E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.839636871372293E-2</v>
+        <v>2.800829107168187E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9676545601161813E-2</v>
+        <v>2.9270972481692595E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0543192581978037E-2</v>
+        <v>2.0262440003450042E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2106337286354468E-2</v>
+        <v>1.1940886595274671E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4817694039280664E-3</v>
+        <v>7.3795201530522606E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3766609286585486E-3</v>
+        <v>5.3031810440900776E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.19</v>
+        <v>-46.83</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.19</v>
+        <v>46.83</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.19</v>
+        <v>46.83</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13647623248050844</v>
+        <v>0.1311887749570162</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FF2405-5F61-43BD-9FA1-1DD6A618DBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B20184-E97A-4ED5-9DA9-259336B33FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>46.83</v>
+        <v>47.09</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23712.27117357</v>
+        <v>23843.92162211</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1311887749570162</v>
+        <v>0.12906849322302461</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>28.630686160261423</v>
+        <v>27.829049692637142</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>40.629719578204039</v>
+        <v>34.890699846411323</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6187899007981183E-2</v>
+        <v>4.593287981617665E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9218449711723255E-2</v>
+        <v>1.9112338076024634E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.5531981370722516</v>
+        <v>1.5262917238225882</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>27.077488023189172</v>
+        <v>26.302757968814554</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>28.630686160261423</v>
+        <v>27.829049692637142</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55758569374556943</v>
+        <v>0.56997294285678701</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>1.9351128270641307</v>
+        <v>1.7567999999999999</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>38.694606751139908</v>
+        <v>33.133899846411325</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>40.629719578204039</v>
+        <v>34.890699846411323</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37217120470370646</v>
+        <v>0.46085313216465762</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9218449711723255E-2</v>
+        <v>1.9112338076024634E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9218449711723255E-2</v>
+        <v>1.9112338076024634E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9218449711723255E-2</v>
+        <v>1.9112338076024634E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6092248558616276E-3</v>
+        <v>9.556169038012317E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6187899007981183E-2</v>
+        <v>4.593287981617665E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.6971263007435083E-2</v>
+        <v>6.6601491752775202E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.6697026092569722E-2</v>
+        <v>6.6328768993736242E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2378490938752927E-2</v>
+        <v>4.2144504792138444E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>3.9748859373931952E-2</v>
+        <v>3.9529392322812336E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.7880385902367934E-2</v>
+        <v>2.7726448753618398E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6588937561382194E-2</v>
+        <v>2.6442130940741729E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6582739887562446E-2</v>
+        <v>1.6491180907507948E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2410875653615983E-2</v>
+        <v>1.2342350963237129E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.120229603386017E-3</v>
+        <v>6.0864377219487613E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.9660508397366305E-3</v>
+        <v>3.9441529162214141E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.870022576393893E-2</v>
+        <v>6.8320908314403475E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8741739048646855E-2</v>
+        <v>7.8306978968955873E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3020648119161851E-2</v>
+        <v>5.2727902981956877E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7299817530167007E-2</v>
+        <v>3.7093872476910615E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.800829107168187E-2</v>
+        <v>2.7853647714734805E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9270972481692595E-2</v>
+        <v>2.9109357428703846E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0262440003450042E-2</v>
+        <v>2.0150564140190386E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1940886595274671E-2</v>
+        <v>1.1874956875275278E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3795201530522606E-3</v>
+        <v>7.3387752976733353E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3031810440900776E-3</v>
+        <v>5.2739003672698731E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.83</v>
+        <v>-47.09</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.83</v>
+        <v>47.09</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5531981370722516</v>
+        <v>1.5262917238225882</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>27.077488023189172</v>
+        <v>26.302757968814554</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>28.630686160261423</v>
+        <v>27.829049692637142</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.55758569374556943</v>
+        <v>0.56997294285678701</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.83</v>
+        <v>47.09</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1311887749570162</v>
+        <v>0.12906849322302461</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.9351128270641307</v>
+        <v>1.7567999999999999</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>38.694606751139908</v>
+        <v>33.133899846411325</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>40.629719578204039</v>
+        <v>34.890699846411323</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.37217120470370646</v>
+        <v>0.46085313216465762</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B20184-E97A-4ED5-9DA9-259336B33FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09A5949-712B-4934-A86C-1582D15E87C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>47.09</v>
+        <v>45.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23843.92162211</v>
+        <v>23236.304167310002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12906849322302461</v>
+        <v>0.13898885234207792</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.593287981617665E-2</v>
+        <v>4.7134001101411166E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9112338076024634E-2</v>
+        <v>1.9612115929396382E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9112338076024634E-2</v>
+        <v>1.9612115929396382E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9112338076024634E-2</v>
+        <v>1.9612115929396382E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9112338076024634E-2</v>
+        <v>1.9612115929396382E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.556169038012317E-3</v>
+        <v>9.8060579646981911E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.593287981617665E-2</v>
+        <v>4.7134001101411166E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.6601491752775202E-2</v>
+        <v>6.8343086655876767E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.6328768993736242E-2</v>
+        <v>6.8063232336348659E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2144504792138444E-2</v>
+        <v>4.3246562010499007E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>3.9529392322812336E-2</v>
+        <v>4.0563065689283792E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.7726448753618398E-2</v>
+        <v>2.8451481189973642E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6442130940741729E-2</v>
+        <v>2.7133579123981875E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6491180907507948E-2</v>
+        <v>1.6922416843202209E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2342350963237129E-2</v>
+        <v>1.2665097120480201E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.0864377219487613E-3</v>
+        <v>6.2455949515486421E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.9441529162214141E-3</v>
+        <v>4.047290495203016E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8320908314403475E-2</v>
+        <v>7.0107465080088471E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8306978968955873E-2</v>
+        <v>8.0354666368449165E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2727902981956877E-2</v>
+        <v>5.4106710643285018E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7093872476910615E-2</v>
+        <v>3.8063858246627169E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7853647714734805E-2</v>
+        <v>2.8582006338785396E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9109357428703846E-2</v>
+        <v>2.9870552218733144E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0150564140190386E-2</v>
+        <v>2.067749107347059E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1874956875275278E-2</v>
+        <v>1.2185480916467919E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3387752976733353E-3</v>
+        <v>7.5306805135636817E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2739003672698731E-3</v>
+        <v>5.4118101611405171E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.09</v>
+        <v>-45.89</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.09</v>
+        <v>45.89</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.09</v>
+        <v>45.89</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12906849322302461</v>
+        <v>0.13898885234207792</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09A5949-712B-4934-A86C-1582D15E87C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B2F9DC-67BA-4123-A8A1-AB5C816762F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>45.89</v>
+        <v>46.29</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23236.304167310002</v>
+        <v>23438.84331891</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13898885234207792</v>
+        <v>0.13564357714946484</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.7134001101411166E-2</v>
+        <v>4.6726707940025029E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9612115929396382E-2</v>
+        <v>1.9442644199611149E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13518,20 +13518,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9612115929396382E-2</v>
+        <v>1.9442644199611149E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9612115929396382E-2</v>
+        <v>1.9442644199611149E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9612115929396382E-2</v>
+        <v>1.9442644199611149E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.8060579646981911E-3</v>
+        <v>9.7213220998055745E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14717,50 +14717,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.7134001101411166E-2</v>
+        <v>4.6726707940025029E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.8343086655876767E-2</v>
+        <v>6.7752522070386359E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.8063232336348659E-2</v>
+        <v>6.7475086021063738E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.3246562010499007E-2</v>
+        <v>4.2872860891376097E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.0563065689283792E-2</v>
+        <v>4.0212553132020594E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8451481189973642E-2</v>
+        <v>2.8205626956316492E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.7133579123981875E-2</v>
+        <v>2.6899113112973175E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6922416843202209E-2</v>
+        <v>1.6776187274455592E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2665097120480201E-2</v>
+        <v>1.2555655797339305E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.2455949515486421E-3</v>
+        <v>6.191625671345154E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.047290495203016E-3</v>
+        <v>4.0123171489493716E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14774,43 +14774,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0107465080088471E-2</v>
+        <v>6.950165419151566E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0354666368449165E-2</v>
+        <v>7.966030761823574E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4106710643285018E-2</v>
+        <v>5.3639165077130041E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8063858246627169E-2</v>
+        <v>3.773494177873668E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8582006338785396E-2</v>
+        <v>2.8335024214449382E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9870552218733144E-2</v>
+        <v>2.9612435543695487E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.067749107347059E-2</v>
+        <v>2.0498813250411869E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2185480916467919E-2</v>
+        <v>1.208018404097457E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5306805135636817E-3</v>
+        <v>7.4656065838720536E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4118101611405171E-3</v>
+        <v>5.365045761389897E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-45.89</v>
+        <v>-46.29</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>45.89</v>
+        <v>46.29</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>45.89</v>
+        <v>46.29</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13898885234207792</v>
+        <v>0.13564357714946484</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B2F9DC-67BA-4123-A8A1-AB5C816762F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F7B307-753B-434F-A941-7E9DFA849C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4240,13 +4244,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4421,7 +4425,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6644,7 +6648,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12814,7 +12818,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19837,4 +19841,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F7B307-753B-434F-A941-7E9DFA849C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45841515-CC39-4EA9-99D6-018507D4053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{35E585F1-693A-427F-8C4E-7CE2DFDD4115}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>506347879</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>46.29</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19844,22 +19953,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C80FF1-8FF2-4046-8CF1-33B94006286E}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45841515-CC39-4EA9-99D6-018507D4053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E888C6A8-13C6-41C6-B3A0-374A2BCFBF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>46.29</v>
+        <v>46.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23438.84331891</v>
+        <v>23545.176373499999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>64.714648137522119</v>
+        <v>52.623089120205158</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13564357714946484</v>
+        <v>6.068870591626796E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>27.829049692637142</v>
+        <v>18.605220097652271</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4638,7 +4638,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>34.890699846411323</v>
+        <v>25.586749713338708</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4657,7 +4657,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>56.741377225429467</v>
+        <v>44.699984953439703</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4676,7 +4676,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>52.676874362859721</v>
+        <v>43.262452230628902</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4713,13 +4713,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4740,13 +4740,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4766,13 +4766,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4801,13 +4801,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4893,13 +4893,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4915,13 +4915,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4937,22 +4937,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6726707940025029E-2</v>
+        <v>4.651568409771524E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9442644199611149E-2</v>
+        <v>1.935483870967742E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5146,22 +5146,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>36.049655175729313</v>
+        <v>28.839724140583449</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5217,13 +5217,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5345,13 +5345,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5390,13 +5390,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>102.01 CNY</v>
+        <v>80.73 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>78.93 CNY</v>
+        <v>63.46 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>62.88 CNY</v>
+        <v>51.28 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>51.55 CNY</v>
+        <v>42.57 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>43.44 CNY</v>
+        <v>36.23 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>64.714648137522119</v>
+        <v>52.623089120205158</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5539,13 +5539,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5558,22 +5558,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.5262917238225882</v>
+        <v>1.3439665422936569</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>26.302757968814554</v>
+        <v>17.261253555358614</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>27.829049692637142</v>
+        <v>18.605220097652271</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.56997294285678701</v>
+        <v>0.64644378715295503</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>1.7567999999999999</v>
+        <v>1.6345015930814752</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>33.133899846411325</v>
+        <v>23.952248120257234</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>34.890699846411323</v>
+        <v>25.586749713338708</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.46085313216465762</v>
+        <v>0.51377332381814844</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.4057107545154754</v>
+        <v>2.340473165884764</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>54.335666470913992</v>
+        <v>42.359511787554936</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>56.741377225429467</v>
+        <v>44.699984953439703</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12320658678617891</v>
+        <v>0.15056326603455328</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>50.386473310255305</v>
+        <v>40.972051178024486</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>52.676874362859721</v>
+        <v>43.262452230628902</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.18451314154115339</v>
+        <v>0.17735690753902755</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5906,13 +5906,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5920,13 +5920,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5949,13 +5949,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5963,22 +5963,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6002,6 +6002,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6018,17 +6029,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13631,20 +13631,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9442644199611149E-2</v>
+        <v>1.935483870967742E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9442644199611149E-2</v>
+        <v>1.935483870967742E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9442644199611149E-2</v>
+        <v>1.935483870967742E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.7213220998055745E-3</v>
+        <v>9.6774193548387101E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14830,50 +14830,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6726707940025029E-2</v>
+        <v>4.651568409771524E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.7752522070386359E-2</v>
+        <v>6.7446542938455589E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.7475086021063738E-2</v>
+        <v>6.71703598261299E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2872860891376097E-2</v>
+        <v>4.2679241519608592E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.0212553132020594E-2</v>
+        <v>4.0030948053359855E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8205626956316492E-2</v>
+        <v>2.8078246705546029E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6899113112973175E-2</v>
+        <v>2.6777633247301681E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6776187274455592E-2</v>
+        <v>1.6700423848054823E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2555655797339305E-2</v>
+        <v>1.2498952835673902E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.191625671345154E-3</v>
+        <v>6.1636634908939173E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>4.0123171489493716E-3</v>
+        <v>3.9941970069863738E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14887,43 +14887,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.950165419151566E-2</v>
+        <v>6.9187775753231401E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.966030761823574E-2</v>
+        <v>7.9300551390282414E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3639165077130041E-2</v>
+        <v>5.3396923686459132E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.773494177873668E-2</v>
+        <v>3.756452591263916E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8335024214449382E-2</v>
+        <v>2.8207059588964772E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9612435543695487E-2</v>
+        <v>2.9478701963820735E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0498813250411869E-2</v>
+        <v>2.0406237964764849E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.208018404097457E-2</v>
+        <v>1.2025628371112105E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4656065838720536E-3</v>
+        <v>7.4318909412352122E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.365045761389897E-3</v>
+        <v>5.3408165224674911E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15694,7 +15694,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15705,16 +15705,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>18253666436.911911</v>
+        <v>14602933149.529528</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15729,8 +15729,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15745,8 +15745,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15761,8 +15761,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>21996281824.804184</v>
+        <v>18345548537.421803</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>64.595614038969885</v>
+        <v>52.589576970989206</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15895,11 +15895,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>1077149183.5478804</v>
+        <v>1062119194.9402356</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15917,11 +15917,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>1059376543.7279025</v>
+        <v>1030018807.5999321</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15939,11 +15939,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1041897147.1568592</v>
+        <v>998888589.02440226</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15971,11 +15971,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1024706155.4087249</v>
+        <v>968699217.84059942</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16003,11 +16003,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1007798809.8900584</v>
+        <v>939422258.8542006</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16035,11 +16035,11 @@
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>991170430.52278924</v>
+        <v>911030136.26666033</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16057,11 +16057,11 @@
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>974816414.4487375</v>
+        <v>883496107.70172632</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16079,11 +16079,11 @@
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>958732234.75550795</v>
+        <v>856794239.01694846</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16101,11 +16101,11 @@
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>942913439.22340834</v>
+        <v>830899379.87646174</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16123,11 +16123,11 @@
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>927355649.09304118</v>
+        <v>805787140.06202817</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16145,11 +16145,11 @@
       </c>
       <c r="E31" s="124">
         <f t="shared" si="0"/>
-        <v>0.52678752539162055</v>
+        <v>0.45134318911764126</v>
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>912054557.85323179</v>
+        <v>781433866.50003207</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16167,11 +16167,11 @@
       </c>
       <c r="E32" s="124">
         <f t="shared" si="0"/>
-        <v>0.4969693635770005</v>
+        <v>0.41985412941175931</v>
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>897005930.04895318</v>
+        <v>757816620.98278713</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -16189,11 +16189,11 @@
       </c>
       <c r="E33" s="124">
         <f t="shared" si="0"/>
-        <v>0.46883902224245327</v>
+        <v>0.39056198084814819</v>
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>882205600.10892165</v>
+        <v>734913158.56317019</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -16221,11 +16221,11 @@
       </c>
       <c r="E34" s="124">
         <f t="shared" si="0"/>
-        <v>0.44230096437967292</v>
+        <v>0.36331347055641694</v>
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>867649471.19253528</v>
+        <v>712701906.60223448</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -16253,11 +16253,11 @@
       </c>
       <c r="E35" s="124">
         <f t="shared" si="0"/>
-        <v>0.41726506073554037</v>
+        <v>0.33796601912224833</v>
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>853333514.0558387</v>
+        <v>691161944.45006597</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -16285,11 +16285,11 @@
       </c>
       <c r="E36" s="124">
         <f t="shared" si="0"/>
-        <v>0.39364628371277405</v>
+        <v>0.31438699453232405</v>
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>839253765.93619859</v>
+        <v>670272983.7407428</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -16307,11 +16307,11 @@
       </c>
       <c r="E37" s="124">
         <f t="shared" si="0"/>
-        <v>0.37136441859695657</v>
+        <v>0.29245301816960378</v>
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>825406329.45538056</v>
+        <v>650015349.28284228</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -16329,11 +16329,11 @@
       </c>
       <c r="E38" s="124">
         <f t="shared" si="0"/>
-        <v>0.35034379112920433</v>
+        <v>0.27204931922753844</v>
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>811787371.54072881</v>
+        <v>630369960.52749097</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -16351,11 +16351,11 @@
       </c>
       <c r="E39" s="124">
         <f t="shared" si="0"/>
-        <v>0.3305130104992493</v>
+        <v>0.25306913416515198</v>
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>798393122.36413956</v>
+        <v>611318313.59650493</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -16373,11 +16373,11 @@
       </c>
       <c r="E40" s="124">
         <f t="shared" si="0"/>
-        <v>0.31180472688608429</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>785219874.29854846</v>
+        <v>592842463.85369623</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -16395,11 +16395,11 @@
       </c>
       <c r="E41" s="124">
         <f t="shared" si="0"/>
-        <v>0.29415540272272095</v>
+        <v>0.21898897494009908</v>
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>772263980.89162898</v>
+        <v>574925009.00292063</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -16417,11 +16417,11 @@
       </c>
       <c r="E42" s="124">
         <f t="shared" si="0"/>
-        <v>0.27750509690822728</v>
+        <v>0.20371067436288287</v>
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>759521855.85643041</v>
+        <v>557549072.69695866</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -16439,11 +16439,11 @@
       </c>
       <c r="E43" s="124">
         <f t="shared" si="0"/>
-        <v>0.26179726123417668</v>
+        <v>0.18949830173291429</v>
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>746989972.07866454</v>
+        <v>540698288.64177871</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -16461,11 +16461,11 @@
       </c>
       <c r="E44" s="124">
         <f t="shared" si="0"/>
-        <v>0.24697854833412897</v>
+        <v>0.17627748998410636</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>734664860.64037597</v>
+        <v>524356785.18122137</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -16483,11 +16483,11 @@
       </c>
       <c r="E45" s="124">
         <f t="shared" si="0"/>
-        <v>0.23299863050389524</v>
+        <v>0.16397906045033148</v>
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>722543109.85971892</v>
+        <v>508509170.34757668</v>
       </c>
       <c r="H45" s="120"/>
     </row>
@@ -16505,11 +16505,11 @@
       </c>
       <c r="E46" s="124">
         <f t="shared" si="0"/>
-        <v>0.21981002877725966</v>
+        <v>0.15253866088402931</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>710621364.34657979</v>
+        <v>493140517.36398011</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -16527,11 +16527,11 @@
       </c>
       <c r="E47" s="124">
         <f t="shared" si="0"/>
-        <v>0.20736795167666003</v>
+        <v>0.14189642872932959</v>
       </c>
       <c r="F47" s="125">
         <f t="shared" si="1"/>
-        <v>698896324.07377934</v>
+        <v>478236350.584966</v>
       </c>
       <c r="G47" s="338"/>
       <c r="H47" s="339"/>
@@ -16559,11 +16559,11 @@
       </c>
       <c r="E48" s="124">
         <f t="shared" si="0"/>
-        <v>0.1956301430911887</v>
+        <v>0.13199667788774846</v>
       </c>
       <c r="F48" s="125">
         <f t="shared" si="1"/>
-        <v>687364743.46360135</v>
+        <v>463782631.86194223</v>
       </c>
       <c r="G48" s="338"/>
       <c r="H48" s="339"/>
@@ -16591,11 +16591,11 @@
       </c>
       <c r="E49" s="124">
         <f t="shared" si="0"/>
-        <v>0.18455673876527234</v>
+        <v>0.1227876073374404</v>
       </c>
       <c r="F49" s="125">
         <f t="shared" si="1"/>
-        <v>676023430.48939252</v>
+        <v>449765747.3207382</v>
       </c>
       <c r="G49" s="338"/>
       <c r="H49" s="339"/>
@@ -16623,11 +16623,11 @@
       </c>
       <c r="E50" s="124">
         <f t="shared" si="0"/>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F50" s="125">
         <f t="shared" si="1"/>
-        <v>664869245.79198575</v>
+        <v>436172494.53877598</v>
       </c>
       <c r="G50" s="338"/>
       <c r="H50" s="339"/>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>19029635576.012558</v>
+        <v>15223708460.810045</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16655,11 +16655,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>3313252341.3212094</v>
+        <v>1738867662.0517333</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>28965236773.442753</v>
+        <v>22886005368.875355</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16691,7 +16691,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>28965236773.442753</v>
+        <v>22886005368.875355</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16721,19 +16721,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>18253666436.911903</v>
+        <v>14602933149.52953</v>
       </c>
       <c r="C56" s="123">
-        <v>18799491744.754734</v>
+        <v>15065999509.581528</v>
       </c>
       <c r="D56" s="123">
-        <v>19359629914.559135</v>
+        <v>15542555896.436546</v>
       </c>
       <c r="E56" s="123">
-        <v>19934713446.61203</v>
+        <v>16033195332.596296</v>
       </c>
       <c r="F56" s="123">
-        <v>20525394514.517418</v>
+        <v>16538529223.03788</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16742,19 +16742,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>18253666436.911903</v>
+        <v>14602933149.52953</v>
       </c>
       <c r="C57" s="123">
-        <v>19314607737.273598</v>
+        <v>15525189225.011539</v>
       </c>
       <c r="D57" s="123">
-        <v>20478081136.358673</v>
+        <v>16539293314.161072</v>
       </c>
       <c r="E57" s="123">
-        <v>21756516979.944885</v>
+        <v>17656273452.404163</v>
       </c>
       <c r="F57" s="123">
-        <v>23163747039.148102</v>
+        <v>18888393265.027225</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16763,19 +16763,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>18253666436.911896</v>
+        <v>14602933149.52953</v>
       </c>
       <c r="C58" s="341">
-        <v>20013084336.720451</v>
+        <v>16106577178.800186</v>
       </c>
       <c r="D58" s="123">
-        <v>22075377498.996925</v>
+        <v>17868425177.806267</v>
       </c>
       <c r="E58" s="123">
-        <v>24501914061.731716</v>
+        <v>19940031411.431042</v>
       </c>
       <c r="F58" s="123">
-        <v>27366348701.915016</v>
+        <v>22383175203.824879</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16794,19 +16794,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>18253666436.911896</v>
+        <v>14602933149.529533</v>
       </c>
       <c r="C59" s="341">
-        <v>20793717528.359291</v>
+        <v>16712683605.701841</v>
       </c>
       <c r="D59" s="123">
-        <v>23961313214.366631</v>
+        <v>19332256282.421768</v>
       </c>
       <c r="E59" s="123">
-        <v>27937473971.007149</v>
+        <v>22605750722.973476</v>
       </c>
       <c r="F59" s="123">
-        <v>32956420591.122528</v>
+        <v>26719071861.747692</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16825,19 +16825,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>18253666436.911892</v>
+        <v>14602933149.529535</v>
       </c>
       <c r="C60" s="341">
-        <v>21590480648.473019</v>
+        <v>17289557035.74567</v>
       </c>
       <c r="D60" s="123">
-        <v>26000040335.82856</v>
+        <v>20807850252.900734</v>
       </c>
       <c r="E60" s="123">
-        <v>31888763693.73177</v>
+        <v>25464596061.979565</v>
       </c>
       <c r="F60" s="123">
-        <v>39823276180.631668</v>
+        <v>31685490230.559006</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16856,19 +16856,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>18253666436.911892</v>
+        <v>14602933149.529537</v>
       </c>
       <c r="C61" s="341">
-        <v>22361954115.932011</v>
+        <v>17810344607.712788</v>
       </c>
       <c r="D61" s="123">
-        <v>28095759300.45348</v>
+        <v>22222091766.730198</v>
       </c>
       <c r="E61" s="123">
-        <v>36225436734.546997</v>
+        <v>28389980831.38665</v>
       </c>
       <c r="F61" s="123">
-        <v>47907714791.933189</v>
+        <v>37136787680.058159</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16948,23 +16948,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16975,23 +16975,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>43.441046634272908</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>44.51901166677348</v>
+        <v>37.14563776710083</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>45.625243554049547</v>
+        <v>38.086801750637569</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>46.760991437873294</v>
+        <v>39.05577872577318</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>47.927543313378216</v>
+        <v>40.053776172586979</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17002,23 +17002,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>43.441046634272908</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>45.536328049210354</v>
+        <v>38.05250384568869</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>47.834102854513873</v>
+        <v>40.055285196629299</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>50.358920073282576</v>
+        <v>42.261239214742396</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>53.138096441084087</v>
+        <v>44.694585662359415</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17029,23 +17029,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>43.441046634272894</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>46.915768209651617</v>
+        <v>39.200702501002198</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>50.988646260112404</v>
+        <v>42.680223344430246</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>55.780878366479719</v>
+        <v>46.771494029154042</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>61.437927124816277</v>
+        <v>51.59652419856814</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17056,23 +17056,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>43.441046634272894</v>
+        <v>36.231115599127072</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>48.457461626400068</v>
+        <v>40.397718331499355</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>54.71323126102974</v>
+        <v>45.571182634131347</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>62.565857729008918</v>
+        <v>52.036094557958542</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>72.477909952921522</v>
+        <v>60.159602741497736</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17083,23 +17083,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>43.441046634272887</v>
+        <v>36.231115599127079</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>50.031010471291602</v>
+        <v>41.537001132847529</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>58.739568105746585</v>
+        <v>48.485372722955567</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>70.369365725385109</v>
+        <v>57.682104855566777</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>86.039447137733433</v>
+        <v>69.967915513775225</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17109,23 +17109,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>43.441046634272887</v>
+        <v>36.231115599127079</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>51.554614103210817</v>
+        <v>42.565518469575856</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>62.878459669317095</v>
+        <v>51.278396200455838</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>78.933977567701575</v>
+        <v>63.459525658008971</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>102.00562167226035</v>
+        <v>80.733828980747901</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>102.00562167226035</v>
+        <v>80.733828980747901</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>78.933977567701575</v>
+        <v>63.459525658008971</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>62.878459669317095</v>
+        <v>51.278396200455838</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>51.554614103210817</v>
+        <v>42.565518469575856</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>43.441046634272887</v>
+        <v>36.231115599127079</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17465,14 +17465,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>7595218185.000001</v>
+        <v>6076174548.000001</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>15.000000000000002</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>23.802262033399185</v>
+        <v>18.806637106008552</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17577,11 +17577,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>448193961.20316249</v>
+        <v>441940091.97707188</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17599,11 +17599,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>440798894.70390928</v>
+        <v>428583353.67382371</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17621,11 +17621,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>433525844.59323376</v>
+        <v>415630295.55560547</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17643,11 +17643,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>426372797.6371668</v>
+        <v>403068717.21180147</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17665,11 +17665,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>419337773.81949806</v>
+        <v>390886786.96433413</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17687,11 +17687,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>412418825.7936939</v>
+        <v>379073030.72347474</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17709,11 +17709,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>405614038.34385622</v>
+        <v>367616321.18046439</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17731,11 +17731,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>398921527.85457766</v>
+        <v>356505867.32676631</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17753,11 +17753,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>392339441.78954244</v>
+        <v>345731204.29007769</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17775,11 +17775,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>385865958.17873049</v>
+        <v>335282183.47752613</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -17797,11 +17797,11 @@
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
-        <v>0.52678752539162055</v>
+        <v>0.45134318911764126</v>
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>379499285.11408305</v>
+        <v>325148963.01676893</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -17819,11 +17819,11 @@
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
-        <v>0.4969693635770005</v>
+        <v>0.41985412941175931</v>
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>373237660.25348932</v>
+        <v>315321998.48599082</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -17841,11 +17841,11 @@
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
-        <v>0.46883902224245327</v>
+        <v>0.39056198084814819</v>
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>367079350.33295673</v>
+        <v>305792033.92406756</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -17863,11 +17863,11 @@
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
-        <v>0.44230096437967292</v>
+        <v>0.36331347055641694</v>
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>361022650.686831</v>
+        <v>296550093.11242998</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -17885,11 +17885,11 @@
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
-        <v>0.41726506073554037</v>
+        <v>0.33796601912224833</v>
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>355065884.77593195</v>
+        <v>287587471.12041551</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -17907,11 +17907,11 @@
       </c>
       <c r="E31" s="124">
         <f t="shared" si="0"/>
-        <v>0.39364628371277405</v>
+        <v>0.31438699453232405</v>
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>349207403.7234754</v>
+        <v>278895726.10614413</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -17929,11 +17929,11 @@
       </c>
       <c r="E32" s="124">
         <f t="shared" si="0"/>
-        <v>0.37136441859695657</v>
+        <v>0.29245301816960378</v>
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>343445585.85865122</v>
+        <v>270466671.36519659</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17951,11 +17951,11 @@
       </c>
       <c r="E33" s="124">
         <f t="shared" si="0"/>
-        <v>0.35034379112920433</v>
+        <v>0.27204931922753844</v>
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>337778836.26773375</v>
+        <v>262292367.61960435</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -17973,11 +17973,11 @@
       </c>
       <c r="E34" s="124">
         <f t="shared" si="0"/>
-        <v>0.3305130104992493</v>
+        <v>0.25306913416515198</v>
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>332205586.35259712</v>
+        <v>254365115.53988987</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -17995,11 +17995,11 @@
       </c>
       <c r="E35" s="124">
         <f t="shared" si="0"/>
-        <v>0.31180472688608429</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>326724293.39651632</v>
+        <v>246677448.49311274</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -18017,11 +18017,11 @@
       </c>
       <c r="E36" s="124">
         <f t="shared" si="0"/>
-        <v>0.29415540272272095</v>
+        <v>0.21898897494009908</v>
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>321333440.13713121</v>
+        <v>239222125.5100908</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -18039,11 +18039,11 @@
       </c>
       <c r="E37" s="124">
         <f t="shared" si="0"/>
-        <v>0.27750509690822728</v>
+        <v>0.20371067436288287</v>
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>316031534.34645772</v>
+        <v>231992124.46517345</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18061,11 +18061,11 @@
       </c>
       <c r="E38" s="124">
         <f t="shared" si="0"/>
-        <v>0.26179726123417668</v>
+        <v>0.18949830173291429</v>
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>310817108.41782796</v>
+        <v>224980635.46214211</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18083,11 +18083,11 @@
       </c>
       <c r="E39" s="124">
         <f t="shared" si="0"/>
-        <v>0.24697854833412897</v>
+        <v>0.17627748998410636</v>
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>305688718.95964533</v>
+        <v>218181054.42000806</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18105,11 +18105,11 @@
       </c>
       <c r="E40" s="124">
         <f t="shared" si="0"/>
-        <v>0.23299863050389524</v>
+        <v>0.16397906045033148</v>
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>300644946.39584363</v>
+        <v>211586976.85266662</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -18127,11 +18127,11 @@
       </c>
       <c r="E41" s="124">
         <f t="shared" si="0"/>
-        <v>0.21981002877725966</v>
+        <v>0.15253866088402931</v>
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>295684394.57293791</v>
+        <v>205192191.83654931</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -18149,11 +18149,11 @@
       </c>
       <c r="E42" s="124">
         <f t="shared" si="0"/>
-        <v>0.20736795167666003</v>
+        <v>0.14189642872932959</v>
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>290805690.37355858</v>
+        <v>198990676.16059005</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -18171,11 +18171,11 @@
       </c>
       <c r="E43" s="124">
         <f t="shared" si="0"/>
-        <v>0.1956301430911887</v>
+        <v>0.13199667788774846</v>
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>286007483.33636272</v>
+        <v>192976588.65299797</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -18193,11 +18193,11 @@
       </c>
       <c r="E44" s="124">
         <f t="shared" si="0"/>
-        <v>0.18455673876527234</v>
+        <v>0.1227876073374404</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>281288445.28221601</v>
+        <v>187144264.67949116</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -18215,11 +18215,11 @@
       </c>
       <c r="E45" s="124">
         <f t="shared" si="0"/>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>276647269.94654328</v>
+        <v>181488210.80781057</v>
       </c>
       <c r="H45" s="120"/>
     </row>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>7918093314.5892048</v>
+        <v>6334474651.6713638</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18237,11 +18237,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>1378620263.5657444</v>
+        <v>723530219.73804009</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18252,7 +18252,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>12052224896.013905</v>
+        <v>9522700809.7501278</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18273,7 +18273,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>12052224896.013905</v>
+        <v>9522700809.7501278</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18303,19 +18303,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>7595218184.9999981</v>
+        <v>6076174548.0000019</v>
       </c>
       <c r="C51" s="123">
-        <v>7822332135.9582491</v>
+        <v>6268853101.149004</v>
       </c>
       <c r="D51" s="123">
-        <v>8055401564.9474831</v>
+        <v>6467144756.5886917</v>
       </c>
       <c r="E51" s="123">
-        <v>8294689650.7486792</v>
+        <v>6671296266.6800041</v>
       </c>
       <c r="F51" s="123">
-        <v>8540467758.0673313</v>
+        <v>6881562032.5985394</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18324,19 +18324,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>7595218184.9999981</v>
+        <v>6076174548.0000019</v>
       </c>
       <c r="C52" s="123">
-        <v>8036668163.5878563</v>
+        <v>6459918610.5935287</v>
       </c>
       <c r="D52" s="123">
-        <v>8520781004.6456509</v>
+        <v>6881879965.3718748</v>
       </c>
       <c r="E52" s="123">
-        <v>9052728884.8768044</v>
+        <v>7346647297.8740339</v>
       </c>
       <c r="F52" s="123">
-        <v>9638267103.9014263</v>
+        <v>7859323413.6164408</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18345,19 +18345,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>7595218184.9999962</v>
+        <v>6076174548.0000019</v>
       </c>
       <c r="C53" s="123">
-        <v>8327299209.5890017</v>
+        <v>6701829920.5441723</v>
       </c>
       <c r="D53" s="123">
-        <v>9185404433.7125854</v>
+        <v>7434922091.7803583</v>
       </c>
       <c r="E53" s="123">
-        <v>10195068694.39953</v>
+        <v>8296902417.3312244</v>
       </c>
       <c r="F53" s="123">
-        <v>11386939168.424952</v>
+        <v>9313476825.8038082</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18366,19 +18366,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>7595218184.9999962</v>
+        <v>6076174548.0000019</v>
       </c>
       <c r="C54" s="123">
-        <v>8652115017.6044426</v>
+        <v>6954026407.839448</v>
       </c>
       <c r="D54" s="123">
-        <v>9970128603.5457382</v>
+        <v>8044011595.1944036</v>
       </c>
       <c r="E54" s="123">
-        <v>11624580249.723</v>
+        <v>9406088884.6696739</v>
       </c>
       <c r="F54" s="123">
-        <v>13712927528.906301</v>
+        <v>11117611970.836481</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18387,19 +18387,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>7595218184.9999952</v>
+        <v>6076174548.0000029</v>
       </c>
       <c r="C55" s="123">
-        <v>8983642371.8453331</v>
+        <v>7194059257.2100344</v>
       </c>
       <c r="D55" s="123">
-        <v>10818428169.043877</v>
+        <v>8657995541.7616997</v>
       </c>
       <c r="E55" s="123">
-        <v>13268683239.112284</v>
+        <v>10595633691.022287</v>
       </c>
       <c r="F55" s="123">
-        <v>16570176324.783398</v>
+        <v>13184102625.713114</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18408,19 +18408,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>7595218184.9999943</v>
+        <v>6076174548.0000019</v>
       </c>
       <c r="C56" s="123">
-        <v>9304646885.0778427</v>
+        <v>7410755187.9041538</v>
       </c>
       <c r="D56" s="123">
-        <v>11690441627.040508</v>
+        <v>9246451176.1924057</v>
       </c>
       <c r="E56" s="123">
-        <v>15073141431.434299</v>
+        <v>11812865071.661102</v>
       </c>
       <c r="F56" s="123">
-        <v>19934052583.193951</v>
+        <v>15452347948.557125</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18470,23 +18470,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>15.000000000000002</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>15.000000000000002</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>15.000000000000002</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>15.000000000000002</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>15.000000000000002</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18497,23 +18497,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>14.999999999999996</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>15.448533430033878</v>
+        <v>12.380526039784209</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>15.908828493280769</v>
+        <v>12.772137545753779</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>16.381404948570307</v>
+        <v>13.17532183576107</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>16.866798721333897</v>
+        <v>13.590581333507549</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18524,23 +18524,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>14.999999999999996</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>15.871831396745826</v>
+        <v>12.757866436315277</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>16.827918824254915</v>
+        <v>13.591209227464493</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>17.878476952950372</v>
+        <v>14.509090691528371</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>19.034872078335351</v>
+        <v>15.521588495913184</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18551,23 +18551,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>14.999999999999993</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>16.445806440494643</v>
+        <v>13.235623567298822</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>18.140501451004567</v>
+        <v>14.683426948412986</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>20.134514465695098</v>
+        <v>16.385775000612227</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>22.488371415544037</v>
+        <v>18.393435051406247</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18578,23 +18578,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>14.999999999999993</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>17.087293887142842</v>
+        <v>13.733693170736966</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>19.690274250256586</v>
+        <v>15.886334136682349</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>22.95769515748875</v>
+        <v>18.576337089129336</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>27.082028181866448</v>
+        <v>21.956469913121687</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18605,23 +18605,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>14.999999999999991</v>
+        <v>12.000000000000005</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>17.742036146349363</v>
+        <v>14.207740479564711</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>21.365603802684983</v>
+        <v>17.098907491941326</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>26.204678225011946</v>
+        <v>20.92560101554664</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>32.724885423650406</v>
+        <v>26.037637704241501</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18631,23 +18631,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>14.999999999999989</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>18.375996564760651</v>
+        <v>14.63569908210113</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>23.087766557111436</v>
+        <v>18.26106429921948</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>29.768351081479103</v>
+        <v>23.329543899720971</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>39.368294822449428</v>
+        <v>30.517256197605452</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>39.368294822449428</v>
+        <v>30.517256197605452</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>29.768351081479103</v>
+        <v>23.329543899720971</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>23.087766557111436</v>
+        <v>18.26106429921948</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>18.375996564760651</v>
+        <v>14.63569908210113</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>14.999999999999989</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18873,7 +18873,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.29</v>
+        <v>-46.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>65.614648137522124</v>
+        <v>53.523089120205157</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18937,11 +18937,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 浙江鼎力(603338.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18962,8 +18962,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18984,8 +18984,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18995,8 +18995,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19009,8 +19009,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19028,8 +19028,8 @@
         <v>0.16445427582528804</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19046,8 +19046,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.21768298308972489</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19064,8 +19064,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.18992961357468019</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19091,21 +19091,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19113,14 +19113,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.29</v>
+        <v>46.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19128,14 +19128,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>43.441046634272922</v>
+        <v>36.231115599127065</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19155,8 +19155,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19166,8 +19166,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19175,14 +19175,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>62.878459669317095</v>
+        <v>51.278396200455838</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19192,8 +19192,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19213,8 +19213,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19224,8 +19224,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19233,14 +19233,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>51.554614103210817</v>
+        <v>42.565518469575856</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19250,8 +19250,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19271,8 +19271,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19282,8 +19282,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19291,14 +19291,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>78.933977567701575</v>
+        <v>63.459525658008971</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19309,8 +19309,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.824794135772734</v>
+        <v>51.972046545790462</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19372,8 +19372,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19383,8 +19383,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19392,14 +19392,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>43.441046634272887</v>
+        <v>36.231115599127079</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19409,8 +19409,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19430,8 +19430,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19441,8 +19441,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19450,14 +19450,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>102.00562167226035</v>
+        <v>80.733828980747901</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19467,8 +19467,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>64.714648137522119</v>
+        <v>52.623089120205158</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>64.595614038969885</v>
+        <v>52.589576970989206</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.11421512240685464</v>
+        <v>0.14045909470764265</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.5262917238225882</v>
+        <v>1.3439665422936569</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>26.302757968814554</v>
+        <v>17.261253555358614</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19683,7 +19683,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>27.829049692637142</v>
+        <v>18.605220097652271</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19694,7 +19694,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.56997294285678701</v>
+        <v>0.64644378715295503</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.29</v>
+        <v>46.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19724,7 +19724,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13564357714946484</v>
+        <v>6.068870591626796E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.7567999999999999</v>
+        <v>1.6345015930814752</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19762,7 +19762,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>33.133899846411325</v>
+        <v>23.952248120257234</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>34.890699846411323</v>
+        <v>25.586749713338708</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.46085313216465762</v>
+        <v>0.51377332381814844</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.4057107545154754</v>
+        <v>2.340473165884764</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>54.335666470913992</v>
+        <v>42.359511787554936</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>56.741377225429467</v>
+        <v>44.699984953439703</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19844,7 +19844,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12320658678617891</v>
+        <v>0.15056326603455328</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>50.386473310255305</v>
+        <v>40.972051178024486</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>52.676874362859721</v>
+        <v>43.262452230628902</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.18451314154115339</v>
+        <v>0.17735690753902755</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19957,19 +19957,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E888C6A8-13C6-41C6-B3A0-374A2BCFBF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D616F754-AD0C-4CF0-894A-7012568A18EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3171,7 +3978,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3920,33 +4727,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3961,10 +4790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{35E585F1-693A-427F-8C4E-7CE2DFDD4115}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{4168CF21-D529-4BDD-92B4-C21E1484ACA7}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4076,7 +4910,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>46.29</v>
+            <v>46.5</v>
           </cell>
         </row>
         <row r="13">
@@ -4101,7 +4935,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4331,6 +5165,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>浙江鼎力</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>506347879</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>603338.SS</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>46.5</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>23545.176373499999</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>IND_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>52.623089120205158</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>6.068870591626796E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>603338.SS (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>18.605220097652271</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>25.586749713338708</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>44.699984953439703</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>43.262452230628902</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>1462055536.8163233</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>213032611</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>-213032611.00000003</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>9271615.2714172397</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-10773913</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-1502297.7285827603</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-194943.10109087895</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-365138309.77193511</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>1588040749.2687776</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>1095219986.2147145</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>4.651568409771524E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>1.935483870967742E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.46232527288881309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.14549955248916155</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.18902580584937359</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.22405670341828193</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.24330033263324671</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.42456310191863128</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.50794527810050039</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.5295422156001708</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.5295422156001706</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>28.839724140583449</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>533481194.11000001</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.0535863113786244</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>5.3145118525683231E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.36488435676778314</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>5078017354.46</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>4150855827.3182759</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>8.1976364461443243</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>125240754.68399999</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.2473413237779159</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>36.231115599127065</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>5.6082458208015922</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.08</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>30</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>80.73 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.06</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>30</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>63.46 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.04</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>30</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>51.28 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.02</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>30</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>42.57 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>30</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>36.23 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>52.623089120205158</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.9</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>603338.SS</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>1.3439665422936569</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>17.261253555358614</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>18.605220097652271</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.64644378715295503</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>1.6345015930814752</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>23.952248120257234</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>25.586749713338708</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.51377332381814844</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>2.340473165884764</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>42.359511787554936</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>44.699984953439703</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>0.15056326603455328</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>2.2904010526044152</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>40.972051178024486</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>43.262452230628902</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.17735690753902755</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4347,24 +6924,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4378,7 +6955,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4387,15 +6964,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>506347879</v>
@@ -4404,7 +6981,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4414,7 +6991,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4427,26 +7004,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>46.5</v>
@@ -4456,17 +7033,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4480,7 +7057,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4494,7 +7071,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4507,71 +7084,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4592,7 +7169,7 @@
         <v>52.623089120205158</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4605,7 +7182,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4616,7 +7193,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4624,7 +7201,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4635,7 +7212,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.45</v>
@@ -4643,7 +7220,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4654,7 +7231,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.3</v>
@@ -4662,7 +7239,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4673,7 +7250,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4681,7 +7258,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4692,7 +7269,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4704,7 +7281,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4712,27 +7289,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4740,17 +7317,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4766,17 +7343,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4789,7 +7366,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4801,17 +7378,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4823,17 +7400,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4848,7 +7425,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4863,7 +7440,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4876,12 +7453,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4893,17 +7470,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4915,17 +7492,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4937,26 +7514,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4969,7 +7546,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4982,7 +7559,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4992,14 +7569,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>1.935483870967742E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5008,18 +7585,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5074,7 +7651,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5085,33 +7662,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5120,7 +7697,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5129,7 +7706,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5141,31 +7718,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5173,7 +7750,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5186,7 +7763,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5198,36 +7775,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5240,7 +7817,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5253,7 +7830,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5262,7 +7839,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5271,12 +7848,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5289,7 +7866,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5302,7 +7879,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5315,12 +7892,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5333,7 +7910,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5345,17 +7922,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5368,7 +7945,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5381,7 +7958,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5389,30 +7966,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5527,7 +8104,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5539,17 +8116,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5558,31 +8135,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5591,7 +8168,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5600,7 +8177,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5613,7 +8190,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5626,7 +8203,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5655,7 +8232,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5668,7 +8245,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5681,7 +8258,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5690,12 +8267,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5724,7 +8301,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5737,7 +8314,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5750,7 +8327,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5759,12 +8336,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5793,7 +8370,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5806,7 +8383,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5819,7 +8396,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5828,12 +8405,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5862,7 +8439,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5875,7 +8452,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5888,7 +8465,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5897,7 +8474,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5906,113 +8483,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6029,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6053,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6118,7 +8695,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6134,7 +8711,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1</v>
@@ -6142,7 +8719,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>7798913979</v>
@@ -6178,7 +8755,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>5114327878</v>
@@ -6214,7 +8791,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>478714939</v>
@@ -6250,7 +8827,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>253881041</v>
@@ -6286,7 +8863,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351">
         <v>255918596</v>
@@ -6316,7 +8893,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351">
         <v>-70283969</v>
@@ -6352,7 +8929,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6368,7 +8945,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6384,7 +8961,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>10773913</v>
@@ -6414,7 +8991,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>156551394</v>
@@ -6444,7 +9021,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>309204387</v>
@@ -6480,7 +9057,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>1629038383</v>
@@ -6516,7 +9093,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>233229</v>
@@ -6552,13 +9129,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351">
         <v>213032611</v>
@@ -6588,7 +9165,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6604,7 +9181,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6620,7 +9197,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>1916547999</v>
@@ -6656,7 +9233,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-178527168</v>
@@ -6692,7 +9269,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-996799146</v>
@@ -6754,15 +9331,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6799,7 +9376,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6836,7 +9413,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6873,7 +9450,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6910,7 +9487,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6947,7 +9524,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6963,12 +9540,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -7017,7 +9594,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7066,7 +9643,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7115,7 +9692,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7164,7 +9741,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7213,7 +9790,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7262,7 +9839,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7311,7 +9888,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7360,7 +9937,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7409,7 +9986,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7458,7 +10035,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7507,7 +10084,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7556,7 +10133,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7605,12 +10182,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7659,7 +10236,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7708,12 +10285,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7762,7 +10339,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7811,7 +10388,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7860,7 +10437,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7909,13 +10486,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7964,7 +10541,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8013,7 +10590,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8062,7 +10639,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8111,7 +10688,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8160,7 +10737,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8215,7 +10792,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8314,7 +10891,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8413,7 +10990,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8429,13 +11006,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8484,7 +11061,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8518,7 +11095,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8552,7 +11129,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8601,7 +11178,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8673,7 +11250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8693,7 +11270,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8709,7 +11286,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8720,27 +11297,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>20196142.69+2309129845.46+18315265.15+122722445.83</f>
@@ -8751,7 +11328,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>5078017354.46</v>
@@ -8762,7 +11339,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>14974286.779999999</v>
@@ -8772,7 +11349,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8783,7 +11360,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>2342136338.9299998</v>
@@ -8793,7 +11370,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8804,7 +11381,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8814,7 +11391,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>208734591.13999999</v>
@@ -8825,7 +11402,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8835,7 +11412,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8846,7 +11423,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>26411605.120000001</v>
@@ -8856,7 +11433,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8867,7 +11444,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8879,7 +11456,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <f>1154749077.73+69993040.32</f>
@@ -8892,7 +11469,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8903,7 +11480,7 @@
         <v>2726149227.4254999</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8921,27 +11498,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>1017151265.9299999</v>
@@ -8950,7 +11527,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8961,7 +11538,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8970,7 +11547,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>40867997.270000003</v>
@@ -8981,7 +11558,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8990,7 +11567,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -9001,7 +11578,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -9010,7 +11587,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -9021,7 +11598,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>1799948914+58349007.87+51120522.33</f>
@@ -9031,7 +11608,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -9042,7 +11619,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9051,7 +11628,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9062,7 +11639,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>783590440.46000004</v>
@@ -9071,7 +11648,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9082,7 +11659,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>83517871.469999999</v>
@@ -9094,7 +11671,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <f>140139590.91+2936428.79+10844760</f>
@@ -9107,7 +11684,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9118,7 +11695,7 @@
         <v>712147957.13799989</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9131,30 +11708,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>110070694.45</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9167,13 +11744,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>2901653.62</v>
@@ -9182,13 +11759,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9201,13 +11778,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>999897.45</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9217,14 +11794,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>111070591.90000001</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9234,14 +11811,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>4411635716.5700006</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9254,7 +11831,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>4522706308.4700003</v>
@@ -9267,24 +11844,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9297,13 +11874,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>378055365.97000003</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9313,13 +11890,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>44355236.240000002</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9329,13 +11906,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9345,13 +11922,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9364,14 +11941,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>422410602.21000004</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9384,14 +11961,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>370532416.04999995</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9404,13 +11981,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>792943018.25999999</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9423,7 +12000,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9434,21 +12011,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9480,20 +12057,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9507,7 +12084,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9521,19 +12098,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9547,7 +12124,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9564,19 +12141,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9587,7 +12164,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9601,19 +12178,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9624,12 +12201,12 @@
         <v>2.8914480193462864E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9640,21 +12217,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9665,12 +12242,12 @@
         <v>4150855827.3182759</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9680,7 +12257,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9690,7 +12267,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9700,7 +12277,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9713,19 +12290,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9736,12 +12313,12 @@
         <v>-463580763.570862</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9752,12 +12329,12 @@
         <v>10.953900061221555</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9765,12 +12342,12 @@
         <v>927161527.14172399</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9778,7 +12355,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9786,19 +12363,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9812,7 +12389,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9826,7 +12403,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9840,7 +12417,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9854,7 +12431,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9865,15 +12442,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9890,7 +12467,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9907,7 +12484,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9924,7 +12501,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9946,7 +12523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9972,7 +12549,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -10025,12 +12602,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -10048,7 +12625,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10062,7 +12639,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>AVERAGE(G4:I4)</f>
@@ -10119,7 +12696,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10174,7 +12751,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10229,7 +12806,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10284,7 +12861,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10341,7 +12918,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10396,7 +12973,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10451,7 +13028,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10508,7 +13085,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10563,7 +13140,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10618,7 +13195,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10673,7 +13250,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10730,7 +13307,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10787,7 +13364,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10795,7 +13372,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10813,14 +13390,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10838,7 +13415,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10914,12 +13491,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10937,7 +13514,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10958,7 +13535,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -11015,7 +13592,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11072,7 +13649,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11133,14 +13710,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -11148,7 +13725,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11208,7 +13785,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11259,7 +13836,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11318,21 +13895,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-224833898</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11382,7 +13959,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>G34</f>
@@ -11390,7 +13967,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11441,7 +14018,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11502,7 +14079,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11625,7 +14202,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11684,21 +14261,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11752,12 +14329,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11775,14 +14352,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11837,7 +14414,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11892,7 +14469,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11949,7 +14526,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -12008,23 +14585,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -12044,14 +14621,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>2.0195487899013917E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12071,7 +14648,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12130,17 +14707,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12195,7 +14772,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12250,7 +14827,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12305,7 +14882,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12360,13 +14937,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12416,7 +14993,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12475,17 +15052,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12510,7 +15087,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12535,7 +15112,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12560,7 +15137,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12590,12 +15167,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12613,7 +15190,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12634,7 +15211,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12691,7 +15268,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12748,7 +15325,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12805,7 +15382,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12862,7 +15439,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12919,7 +15496,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12927,7 +15504,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12978,7 +15555,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -13035,7 +15612,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13092,7 +15669,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13149,7 +15726,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13264,7 +15841,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13321,7 +15898,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13347,7 +15924,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13371,7 +15948,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13432,7 +16009,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13551,7 +16128,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13606,7 +16183,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0.1</v>
@@ -13627,7 +16204,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13686,7 +16263,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13707,7 +16284,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13764,7 +16341,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13824,12 +16401,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13847,17 +16424,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13914,7 +16491,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13971,7 +16548,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -14028,7 +16605,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14085,7 +16662,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14146,14 +16723,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14169,7 +16746,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14226,7 +16803,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14283,7 +16860,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14314,14 +16891,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14373,7 +16950,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14429,7 +17006,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14483,7 +17060,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14537,7 +17114,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14591,7 +17168,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14648,7 +17225,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14724,12 +17301,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14747,7 +17324,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14826,7 +17403,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14882,7 +17459,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15627,7 +18204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15644,32 +18221,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15680,7 +18257,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15690,7 +18267,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15701,7 +18278,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15711,15 +18288,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15729,13 +18306,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15745,13 +18322,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15761,13 +18338,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15781,7 +18358,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15795,7 +18372,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15812,7 +18389,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15822,13 +18399,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15838,7 +18415,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15848,7 +18425,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15865,19 +18442,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16643,7 +19220,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16666,7 +19243,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16680,7 +19257,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16901,7 +19478,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17130,19 +19707,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17267,20 +19844,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17387,7 +19964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17404,32 +19981,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17440,7 +20017,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17450,7 +20027,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17461,7 +20038,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17471,13 +20048,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17494,7 +20071,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17504,13 +20081,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17520,7 +20097,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17530,7 +20107,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17547,19 +20124,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18225,7 +20802,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18248,7 +20825,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18262,7 +20839,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18433,7 +21010,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18652,19 +21229,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18789,20 +21366,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18838,7 +21415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18853,20 +21430,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18878,14 +21455,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18907,14 +21484,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18927,7 +21504,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18937,11 +21514,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 浙江鼎力(603338.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18952,7 +21529,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18962,8 +21539,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18974,7 +21551,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18984,8 +21561,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18995,8 +21572,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19007,10 +21584,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>444</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>424</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19021,15 +21598,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.16445427582528804</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19040,14 +21617,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.21768298308972489</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19058,18 +21635,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.18992961357468019</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19078,38 +21655,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19119,12 +21696,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19134,44 +21711,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19181,55 +21758,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19239,55 +21816,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19297,24 +21874,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19327,7 +21904,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19336,12 +21913,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>30</v>
@@ -19356,39 +21933,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19398,55 +21975,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19456,23 +22033,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19483,7 +22060,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19492,7 +22069,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19501,15 +22078,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19517,24 +22094,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>4.25103165866728E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19545,20 +22122,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19568,19 +22145,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19590,14 +22167,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19606,7 +22183,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19615,12 +22192,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19630,7 +22207,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19643,12 +22220,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19657,7 +22234,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19669,7 +22246,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19679,7 +22256,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19690,7 +22267,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19702,12 +22279,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19720,7 +22297,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19732,12 +22309,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19746,7 +22323,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19758,7 +22335,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19768,7 +22345,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19779,7 +22356,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19788,14 +22365,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19806,7 +22383,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19818,7 +22395,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19830,17 +22407,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>44.699984953439703</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19852,12 +22429,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19866,7 +22443,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19876,7 +22453,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19886,17 +22463,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>43.262452230628902</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19908,32 +22485,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19952,24 +22529,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C80FF1-8FF2-4046-8CF1-33B94006286E}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538034BF-5890-4C7B-94D1-41EB4223C6D7}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D616F754-AD0C-4CF0-894A-7012568A18EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFC902D-0717-4012-BF67-C5A0660D93C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4754,8 +4754,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4766,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4790,11 +4795,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>46.5</v>
+        <v>46.47</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>23545.176373499999</v>
+        <v>23529.985937130001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.068870591626796E-2</v>
+        <v>6.0921069533114158E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5577,13 +5577,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5595,13 +5595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5621,13 +5621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5678,13 +5678,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5770,7 +5770,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.651568409771524E-2</v>
+        <v>4.6545713590354178E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.935483870967742E-2</v>
+        <v>1.936733376371853E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5951,13 +5951,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6245,13 +6245,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,13 +6413,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6761,7 +6761,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6804,13 +6804,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>46.5</v>
+        <v>46.47</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23545.176373499999</v>
+        <v>23529.985937130001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.068870591626796E-2</v>
+        <v>6.0921069533114158E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7299,13 +7299,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7317,13 +7317,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7343,13 +7343,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7378,13 +7378,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7400,13 +7400,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7470,13 +7470,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7492,7 +7492,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.651568409771524E-2</v>
+        <v>4.6545713590354178E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.935483870967742E-2</v>
+        <v>1.936733376371853E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7673,13 +7673,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7967,13 +7967,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,13 +8135,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8483,7 +8483,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8526,13 +8526,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16208,20 +16208,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.935483870967742E-2</v>
+        <v>1.936733376371853E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.935483870967742E-2</v>
+        <v>1.936733376371853E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.935483870967742E-2</v>
+        <v>1.936733376371853E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6774193548387101E-3</v>
+        <v>9.6836668818592649E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17407,50 +17407,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.651568409771524E-2</v>
+        <v>4.6545713590354178E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.7446542938455589E-2</v>
+        <v>6.7490084928732194E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.71703598261299E-2</v>
+        <v>6.7213723518722623E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2679241519608592E-2</v>
+        <v>4.2706794290118345E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.0030948053359855E-2</v>
+        <v>4.0056791144420768E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8078246705546029E-2</v>
+        <v>2.8096373398060908E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6777633247301681E-2</v>
+        <v>2.6794920292651781E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6700423848054823E-2</v>
+        <v>1.6711205270810187E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2498952835673902E-2</v>
+        <v>1.2507021882049418E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.1636634908939173E-3</v>
+        <v>6.1676426151617645E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.9941970069863738E-3</v>
+        <v>3.9967755718714531E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17464,43 +17464,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9187775753231401E-2</v>
+        <v>6.9232441844744128E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9300551390282414E-2</v>
+        <v>7.9351746065163153E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3396923686459132E-2</v>
+        <v>5.3431395554558843E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.756452591263916E-2</v>
+        <v>3.7588776736340021E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8207059588964772E-2</v>
+        <v>2.8225269440216524E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9478701963820735E-2</v>
+        <v>2.9497732759149214E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0406237964764849E-2</v>
+        <v>2.0419411778815694E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2025628371112105E-2</v>
+        <v>1.203339184972483E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4318909412352122E-3</v>
+        <v>7.4366888049803605E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3408165224674911E-3</v>
+        <v>5.3442644350062043E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18288,10 +18288,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18306,8 +18306,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18322,8 +18322,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18338,8 +18338,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -20048,8 +20048,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.5</v>
+        <v>-46.47</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21514,11 +21514,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 浙江鼎力(603338.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21539,8 +21539,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21561,8 +21561,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21572,8 +21572,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21586,8 +21586,8 @@
       <c r="B11" s="159" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21605,8 +21605,8 @@
         <v>0.16445427582528804</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21623,8 +21623,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.21768298308972489</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21641,8 +21641,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.18992961357468019</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21668,21 +21668,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21690,14 +21690,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.5</v>
+        <v>46.47</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21711,8 +21711,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21732,8 +21732,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21743,8 +21743,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21758,8 +21758,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21769,8 +21769,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21790,8 +21790,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21801,8 +21801,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21816,8 +21816,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21827,8 +21827,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21848,8 +21848,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21859,8 +21859,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21874,8 +21874,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21886,8 +21886,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21949,8 +21949,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21960,8 +21960,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21975,8 +21975,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21986,8 +21986,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -22007,8 +22007,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -22018,8 +22018,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -22033,8 +22033,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -22044,8 +22044,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.5</v>
+        <v>46.47</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22301,7 +22301,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.068870591626796E-2</v>
+        <v>6.0921069533114158E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22534,19 +22534,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFC902D-0717-4012-BF67-C5A0660D93C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32913A-04E9-4202-B40E-5674A58BF914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4780,7 +4771,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>46.47</v>
+        <v>46.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>23529.985937130001</v>
+        <v>23747.715525099997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.0921069533114158E-2</v>
+        <v>5.7609727051835868E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6545713590354178E-2</v>
+        <v>4.6118961845282705E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.936733376371853E-2</v>
+        <v>1.9189765458422176E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,15 +6857,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6878,12 +6875,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>46.47</v>
+        <v>46.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23529.985937130001</v>
+        <v>23747.715525099997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.0921069533114158E-2</v>
+        <v>5.7609727051835868E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6545713590354178E-2</v>
+        <v>4.6118961845282705E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.936733376371853E-2</v>
+        <v>1.9189765458422176E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,17 +8579,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8606,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16208,20 +16208,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.936733376371853E-2</v>
+        <v>1.9189765458422176E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.936733376371853E-2</v>
+        <v>1.9189765458422176E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.936733376371853E-2</v>
+        <v>1.9189765458422176E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.6836668818592649E-3</v>
+        <v>9.5948827292110881E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17407,50 +17407,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6545713590354178E-2</v>
+        <v>4.6118961845282705E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.7490084928732194E-2</v>
+        <v>6.6871305898468764E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.7213723518722623E-2</v>
+        <v>6.6597478292431567E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2706794290118345E-2</v>
+        <v>4.2315239459739862E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>4.0056791144420768E-2</v>
+        <v>3.9689532718149963E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.8096373398060908E-2</v>
+        <v>2.7838773386095746E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6794920292651781E-2</v>
+        <v>2.6549252579947297E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6711205270810187E-2</v>
+        <v>1.6557989529521307E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2507021882049418E-2</v>
+        <v>1.2392351958610584E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.1676426151617645E-3</v>
+        <v>6.1110949323361875E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.9967755718714531E-3</v>
+        <v>3.9601313608713523E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17464,43 +17464,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9232441844744128E-2</v>
+        <v>6.8597688113544997E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9351746065163153E-2</v>
+        <v>7.8624214064992162E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3431395554558843E-2</v>
+        <v>5.2941512823461614E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7588776736340021E-2</v>
+        <v>3.7244146160718992E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8225269440216524E-2</v>
+        <v>2.7966487652171898E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9497732759149214E-2</v>
+        <v>2.9227284463063202E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0419411778815694E-2</v>
+        <v>2.0232197555683697E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.203339184972483E-2</v>
+        <v>1.1923064376475754E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4366888049803605E-3</v>
+        <v>7.3685059438686014E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3442644350062043E-3</v>
+        <v>5.2952658485018837E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.47</v>
+        <v>-46.9</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.47</v>
+        <v>46.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.47</v>
+        <v>46.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22301,7 +22301,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.0921069533114158E-2</v>
+        <v>5.7609727051835868E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32913A-04E9-4202-B40E-5674A58BF914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00062FF4-2A5C-4B2A-89E6-0096B91A3820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4762,6 +4762,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4771,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>46.9</v>
+        <v>47.85</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>23747.715525099997</v>
+        <v>24228.74601015</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.7609727051835868E-2</v>
+        <v>5.0437078213680486E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6118961845282705E-2</v>
+        <v>4.5203329373955249E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9189765458422176E-2</v>
+        <v>1.8808777429467086E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>46.9</v>
+        <v>47.85</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>23747.715525099997</v>
+        <v>24228.74601015</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.7609727051835868E-2</v>
+        <v>5.0437078213680486E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.6118961845282705E-2</v>
+        <v>4.5203329373955249E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.9189765458422176E-2</v>
+        <v>1.8808777429467086E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16208,20 +16208,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9189765458422176E-2</v>
+        <v>1.8808777429467086E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9189765458422176E-2</v>
+        <v>1.8808777429467086E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9189765458422176E-2</v>
+        <v>1.8808777429467086E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.5948827292110881E-3</v>
+        <v>9.4043887147335428E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17407,50 +17407,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6118961845282705E-2</v>
+        <v>4.5203329373955249E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.6871305898468764E-2</v>
+        <v>6.554366241668097E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.6597478292431567E-2</v>
+        <v>6.5275271304389551E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.2315239459739862E-2</v>
+        <v>4.1475124987707404E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>3.9689532718149963E-2</v>
+        <v>3.8901548265020548E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.7838773386095746E-2</v>
+        <v>2.7286070466204605E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6549252579947297E-2</v>
+        <v>2.6022151431547087E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6557989529521307E-2</v>
+        <v>1.6229252015351085E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2392351958610584E-2</v>
+        <v>1.2146317802692506E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>6.1110949323361875E-3</v>
+        <v>5.9897670287683835E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.9601313608713523E-3</v>
+        <v>3.8815080632155986E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17464,43 +17464,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8597688113544997E-2</v>
+        <v>6.7235769540757773E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8624214064992162E-2</v>
+        <v>7.7063231758581652E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2941512823461614E-2</v>
+        <v>5.1890427406903854E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7244146160718992E-2</v>
+        <v>3.6504711701937739E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7966487652171898E-2</v>
+        <v>2.7411249130341941E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9227284463063202E-2</v>
+        <v>2.8647014447600084E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0232197555683697E-2</v>
+        <v>1.9830513382686842E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1923064376475754E-2</v>
+        <v>1.1686347319889505E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3685059438686014E-3</v>
+        <v>7.2222137673445637E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2952658485018837E-3</v>
+        <v>5.1901351785734236E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-46.9</v>
+        <v>-47.85</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>46.9</v>
+        <v>47.85</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>46.9</v>
+        <v>47.85</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22301,7 +22301,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.7609727051835868E-2</v>
+        <v>5.0437078213680486E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00062FF4-2A5C-4B2A-89E6-0096B91A3820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D795714E-CA0D-41C9-8D5E-337D9BD7F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4780,7 +4771,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>47.85</v>
+        <v>48.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>24228.74601015</v>
+        <v>24360.39645869</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.0437078213680486E-2</v>
+        <v>4.8507456316446929E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.5203329373955249E-2</v>
+        <v>4.4959037841275383E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.8808777429467086E-2</v>
+        <v>1.8707129494907503E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,15 +6857,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6878,12 +6875,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>47.85</v>
+        <v>48.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24228.74601015</v>
+        <v>24360.39645869</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>5.0437078213680486E-2</v>
+        <v>4.8507456316446929E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.5203329373955249E-2</v>
+        <v>4.4959037841275383E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.8808777429467086E-2</v>
+        <v>1.8707129494907503E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,17 +8579,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8606,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16208,20 +16208,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.8808777429467086E-2</v>
+        <v>1.8707129494907503E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.8808777429467086E-2</v>
+        <v>1.8707129494907503E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.8808777429467086E-2</v>
+        <v>1.8707129494907503E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.4043887147335428E-3</v>
+        <v>9.3535647474537516E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17407,50 +17407,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.5203329373955249E-2</v>
+        <v>4.4959037841275383E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.554366241668097E-2</v>
+        <v>6.5189445991232275E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.5275271304389551E-2</v>
+        <v>6.4922505340158809E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.1475124987707404E-2</v>
+        <v>4.1250981722340457E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>3.8901548265020548E-2</v>
+        <v>3.869131333363611E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>2.7286070466204605E-2</v>
+        <v>2.713860885071483E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>2.6022151431547087E-2</v>
+        <v>2.5881520390761342E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>1.6229252015351085E-2</v>
+        <v>1.614154456317916E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>1.2146317802692506E-2</v>
+        <v>1.2080675677797473E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>5.9897670287683835E-3</v>
+        <v>5.9573966395046179E-3</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>3.8815080632155986E-3</v>
+        <v>3.8605312996230806E-3</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17464,43 +17464,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7235769540757773E-2</v>
+        <v>6.6872408491483265E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7063231758581652E-2</v>
+        <v>7.6646760333571651E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1890427406903854E-2</v>
+        <v>5.1609996911668045E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6504711701937739E-2</v>
+        <v>3.6307429950898376E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7411249130341941E-2</v>
+        <v>2.7263111014069051E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8647014447600084E-2</v>
+        <v>2.8492197907247229E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9830513382686842E-2</v>
+        <v>1.9723343699055609E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1686347319889505E-2</v>
+        <v>1.1623191005128099E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2222137673445637E-3</v>
+        <v>7.1831828885353857E-3</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1901351785734236E-3</v>
+        <v>5.1620862252076145E-3</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.85</v>
+        <v>-48.11</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.85</v>
+        <v>48.11</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.85</v>
+        <v>48.11</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22301,7 +22301,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>5.0437078213680486E-2</v>
+        <v>4.8507456316446929E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603338.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603338.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D795714E-CA0D-41C9-8D5E-337D9BD7F57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D9BB81-9D8A-454C-976B-0EB1CEF135C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,6 +4762,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4771,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>48.11</v>
+        <v>48.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>24360.39645869</v>
+        <v>24633.82431335</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>4.8507456316446929E-2</v>
+        <v>4.4544369029294151E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.4959037841275383E-2</v>
+        <v>4.4460006383222173E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.8707129494907503E-2</v>
+        <v>1.8499486125385406E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>48.11</v>
+        <v>48.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>24360.39645869</v>
+        <v>24633.82431335</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>4.8507456316446929E-2</v>
+        <v>4.4544369029294151E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.4959037841275383E-2</v>
+        <v>4.4460006383222173E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>1.8707129494907503E-2</v>
+        <v>1.8499486125385406E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16208,20 +16208,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.8707129494907503E-2</v>
+        <v>1.8499486125385406E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.8707129494907503E-2</v>
+        <v>1.8499486125385406E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>1.8707129494907503E-2</v>
+        <v>1.8499486125385406E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>9.3535647474537516E-3</v>
+        <v>9.249743062692703E-3</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -17407,50 +17407,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4959037841275383E-2</v>
+        <v>4.4460006383222173E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.5189445991232275E-2</v>
+        <v>6.4465863240250457E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.4922505340158809E-2</v>
+        <v>6.4201885548099497E-2</v>
       </c>
  